--- a/VerveStacks_JPN_grids/SysSettings.xlsx
+++ b/VerveStacks_JPN_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4E400DD-04AD-42D0-9B5E-04CB7191F6A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AD2B353-9D77-495B-B2E8-99099CEF6810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11804,7 +11804,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F47ABFF5-E5E8-468C-9319-E5ADE10A2B35}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07ED3984-F30D-4D09-A743-7B883537ADE5}">
   <dimension ref="B3:H191"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SysSettings.xlsx
+++ b/VerveStacks_JPN_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AD2B353-9D77-495B-B2E8-99099CEF6810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE763AD1-B4F1-4A50-A075-E995ADBBD6B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11804,7 +11804,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07ED3984-F30D-4D09-A743-7B883537ADE5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68765522-BF05-4BB0-A4F8-50558C544755}">
   <dimension ref="B3:H191"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SysSettings.xlsx
+++ b/VerveStacks_JPN_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE763AD1-B4F1-4A50-A075-E995ADBBD6B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6020AA8-8FA7-4E48-8EE1-313B919DB633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11804,7 +11804,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68765522-BF05-4BB0-A4F8-50558C544755}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8EBE549-4C2B-47BD-B1B3-059296B21F87}">
   <dimension ref="B3:H191"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SysSettings.xlsx
+++ b/VerveStacks_JPN_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6020AA8-8FA7-4E48-8EE1-313B919DB633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52DA2225-98BF-4EEC-A8CC-E5A19F57328B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11804,7 +11804,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8EBE549-4C2B-47BD-B1B3-059296B21F87}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F32EE0AE-0B4A-4B20-B1E8-47F0A0450260}">
   <dimension ref="B3:H191"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SysSettings.xlsx
+++ b/VerveStacks_JPN_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52DA2225-98BF-4EEC-A8CC-E5A19F57328B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D9908AF-C2D5-4AE8-84E4-7344206C2DA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11804,7 +11804,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F32EE0AE-0B4A-4B20-B1E8-47F0A0450260}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{051F10CD-617D-46B2-B940-C18AB59E8D39}">
   <dimension ref="B3:H191"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SysSettings.xlsx
+++ b/VerveStacks_JPN_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D9908AF-C2D5-4AE8-84E4-7344206C2DA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C887AB8E-C4C1-4B2A-962A-68632A8E31AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11804,7 +11804,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{051F10CD-617D-46B2-B940-C18AB59E8D39}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{588145F0-C5A7-48EF-B536-225AFB911A75}">
   <dimension ref="B3:H191"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SysSettings.xlsx
+++ b/VerveStacks_JPN_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C887AB8E-C4C1-4B2A-962A-68632A8E31AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFB2ACF6-3248-4640-8E5A-EF50AD5F19E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11804,7 +11804,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{588145F0-C5A7-48EF-B536-225AFB911A75}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB68FBE2-74C3-487C-8047-31B47B4C3198}">
   <dimension ref="B3:H191"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SysSettings.xlsx
+++ b/VerveStacks_JPN_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFB2ACF6-3248-4640-8E5A-EF50AD5F19E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75CB8D20-D41F-4E4B-B0CE-556774D786B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11804,7 +11804,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB68FBE2-74C3-487C-8047-31B47B4C3198}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2842FBB0-45FD-4250-B980-784023EB8C46}">
   <dimension ref="B3:H191"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SysSettings.xlsx
+++ b/VerveStacks_JPN_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75CB8D20-D41F-4E4B-B0CE-556774D786B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1935D293-8399-4B2F-8F2E-9451691425C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11804,7 +11804,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2842FBB0-45FD-4250-B980-784023EB8C46}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{330CDF69-464D-40E4-A3D8-0E4F8E6BCF44}">
   <dimension ref="B3:H191"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SysSettings.xlsx
+++ b/VerveStacks_JPN_grids/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{858F2685-288C-4BF3-B9F9-299097BA2778}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BD9EB72-249C-4294-90A6-F1426694E180}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3308" yWindow="3308" windowWidth="21600" windowHeight="12682" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2259" uniqueCount="721">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2505" uniqueCount="803">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -872,16 +872,268 @@
     <t>solar electricity generation in cluster -- 31</t>
   </si>
   <si>
-    <t>elc_spv_032</t>
-  </si>
-  <si>
-    <t>solar electricity generation in cluster -- 32</t>
-  </si>
-  <si>
-    <t>elc_spv_033</t>
-  </si>
-  <si>
-    <t>solar electricity generation in cluster -- 33</t>
+    <t>elc_wof_001</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 1</t>
+  </si>
+  <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 2</t>
+  </si>
+  <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 3</t>
+  </si>
+  <si>
+    <t>elc_wof_004</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 4</t>
+  </si>
+  <si>
+    <t>elc_wof_005</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 5</t>
+  </si>
+  <si>
+    <t>elc_wof_006</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 6</t>
+  </si>
+  <si>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 7</t>
+  </si>
+  <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 8</t>
+  </si>
+  <si>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 9</t>
+  </si>
+  <si>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 10</t>
+  </si>
+  <si>
+    <t>elc_wof_011</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 11</t>
+  </si>
+  <si>
+    <t>elc_wof_012</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 12</t>
+  </si>
+  <si>
+    <t>elc_wof_013</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 13</t>
+  </si>
+  <si>
+    <t>elc_wof_014</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 14</t>
+  </si>
+  <si>
+    <t>elc_wof_015</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 15</t>
+  </si>
+  <si>
+    <t>elc_wof_016</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 16</t>
+  </si>
+  <si>
+    <t>elc_wof_017</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 17</t>
+  </si>
+  <si>
+    <t>elc_wof_018</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 18</t>
+  </si>
+  <si>
+    <t>elc_wof_019</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 19</t>
+  </si>
+  <si>
+    <t>elc_wof_020</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 20</t>
+  </si>
+  <si>
+    <t>elc_wof_021</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 21</t>
+  </si>
+  <si>
+    <t>elc_wof_022</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 22</t>
+  </si>
+  <si>
+    <t>elc_wof_023</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 23</t>
+  </si>
+  <si>
+    <t>elc_wof_024</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 24</t>
+  </si>
+  <si>
+    <t>elc_wof_025</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 25</t>
+  </si>
+  <si>
+    <t>elc_wof_026</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 26</t>
+  </si>
+  <si>
+    <t>elc_wof_027</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 27</t>
+  </si>
+  <si>
+    <t>elc_wof_028</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 28</t>
+  </si>
+  <si>
+    <t>elc_wof_029</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 29</t>
+  </si>
+  <si>
+    <t>elc_wof_030</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 30</t>
+  </si>
+  <si>
+    <t>elc_wof_031</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 31</t>
+  </si>
+  <si>
+    <t>elc_wof_032</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 32</t>
+  </si>
+  <si>
+    <t>elc_wof_033</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 33</t>
+  </si>
+  <si>
+    <t>elc_wof_034</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 34</t>
+  </si>
+  <si>
+    <t>elc_wof_035</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 35</t>
+  </si>
+  <si>
+    <t>elc_wof_036</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 36</t>
+  </si>
+  <si>
+    <t>elc_wof_037</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 37</t>
+  </si>
+  <si>
+    <t>elc_wof_038</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 38</t>
+  </si>
+  <si>
+    <t>elc_wof_039</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 39</t>
+  </si>
+  <si>
+    <t>elc_wof_040</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 40</t>
+  </si>
+  <si>
+    <t>elc_wof_041</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 41</t>
+  </si>
+  <si>
+    <t>elc_wof_042</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 42</t>
+  </si>
+  <si>
+    <t>elc_wof_043</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 43</t>
+  </si>
+  <si>
+    <t>elc_wof_044</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 44</t>
   </si>
   <si>
     <t>elc_won_001</t>
@@ -1064,16 +1316,10 @@
     <t>onshore wind electricity generation in cluster -- 30</t>
   </si>
   <si>
-    <t>elc_won_032</t>
-  </si>
-  <si>
-    <t>onshore wind electricity generation in cluster -- 32</t>
-  </si>
-  <si>
-    <t>elc_won_033</t>
-  </si>
-  <si>
-    <t>onshore wind electricity generation in cluster -- 33</t>
+    <t>elc_won_031</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 31</t>
   </si>
   <si>
     <t>~fi_comm</t>
@@ -4616,13 +4862,13 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29EA57B7-39F1-4323-B189-04DF083D64C8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D56F767-9A8C-483E-8E5B-C8746E992E0C}">
   <dimension ref="B3:H191"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="3" spans="2:8">
       <c r="B3" t="s">
-        <v>345</v>
+        <v>427</v>
       </c>
     </row>
     <row r="4" spans="2:8">
@@ -4653,10 +4899,10 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>346</v>
+        <v>428</v>
       </c>
       <c r="D5" t="s">
-        <v>347</v>
+        <v>429</v>
       </c>
       <c r="E5" t="s">
         <v>25</v>
@@ -4665,7 +4911,7 @@
         <v>35</v>
       </c>
       <c r="G5" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H5" t="s">
         <v>216</v>
@@ -4676,10 +4922,10 @@
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>349</v>
+        <v>431</v>
       </c>
       <c r="D6" t="s">
-        <v>350</v>
+        <v>432</v>
       </c>
       <c r="E6" t="s">
         <v>25</v>
@@ -4688,7 +4934,7 @@
         <v>35</v>
       </c>
       <c r="G6" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H6" t="s">
         <v>216</v>
@@ -4699,10 +4945,10 @@
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>351</v>
+        <v>433</v>
       </c>
       <c r="D7" t="s">
-        <v>352</v>
+        <v>434</v>
       </c>
       <c r="E7" t="s">
         <v>25</v>
@@ -4711,7 +4957,7 @@
         <v>35</v>
       </c>
       <c r="G7" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H7" t="s">
         <v>216</v>
@@ -4722,10 +4968,10 @@
         <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>353</v>
+        <v>435</v>
       </c>
       <c r="D8" t="s">
-        <v>354</v>
+        <v>436</v>
       </c>
       <c r="E8" t="s">
         <v>25</v>
@@ -4734,7 +4980,7 @@
         <v>35</v>
       </c>
       <c r="G8" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H8" t="s">
         <v>216</v>
@@ -4745,10 +4991,10 @@
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>355</v>
+        <v>437</v>
       </c>
       <c r="D9" t="s">
-        <v>356</v>
+        <v>438</v>
       </c>
       <c r="E9" t="s">
         <v>25</v>
@@ -4757,7 +5003,7 @@
         <v>35</v>
       </c>
       <c r="G9" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H9" t="s">
         <v>216</v>
@@ -4768,10 +5014,10 @@
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>357</v>
+        <v>439</v>
       </c>
       <c r="D10" t="s">
-        <v>358</v>
+        <v>440</v>
       </c>
       <c r="E10" t="s">
         <v>25</v>
@@ -4780,7 +5026,7 @@
         <v>35</v>
       </c>
       <c r="G10" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H10" t="s">
         <v>216</v>
@@ -4791,10 +5037,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>359</v>
+        <v>441</v>
       </c>
       <c r="D11" t="s">
-        <v>360</v>
+        <v>442</v>
       </c>
       <c r="E11" t="s">
         <v>25</v>
@@ -4803,7 +5049,7 @@
         <v>35</v>
       </c>
       <c r="G11" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H11" t="s">
         <v>216</v>
@@ -4814,10 +5060,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>361</v>
+        <v>443</v>
       </c>
       <c r="D12" t="s">
-        <v>362</v>
+        <v>444</v>
       </c>
       <c r="E12" t="s">
         <v>25</v>
@@ -4826,7 +5072,7 @@
         <v>35</v>
       </c>
       <c r="G12" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H12" t="s">
         <v>216</v>
@@ -4837,10 +5083,10 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>363</v>
+        <v>445</v>
       </c>
       <c r="D13" t="s">
-        <v>364</v>
+        <v>446</v>
       </c>
       <c r="E13" t="s">
         <v>25</v>
@@ -4849,7 +5095,7 @@
         <v>35</v>
       </c>
       <c r="G13" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H13" t="s">
         <v>216</v>
@@ -4860,10 +5106,10 @@
         <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>365</v>
+        <v>447</v>
       </c>
       <c r="D14" t="s">
-        <v>366</v>
+        <v>448</v>
       </c>
       <c r="E14" t="s">
         <v>25</v>
@@ -4872,7 +5118,7 @@
         <v>35</v>
       </c>
       <c r="G14" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H14" t="s">
         <v>216</v>
@@ -4883,10 +5129,10 @@
         <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>367</v>
+        <v>449</v>
       </c>
       <c r="D15" t="s">
-        <v>368</v>
+        <v>450</v>
       </c>
       <c r="E15" t="s">
         <v>25</v>
@@ -4895,7 +5141,7 @@
         <v>35</v>
       </c>
       <c r="G15" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H15" t="s">
         <v>216</v>
@@ -4906,10 +5152,10 @@
         <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>369</v>
+        <v>451</v>
       </c>
       <c r="D16" t="s">
-        <v>370</v>
+        <v>452</v>
       </c>
       <c r="E16" t="s">
         <v>25</v>
@@ -4918,7 +5164,7 @@
         <v>35</v>
       </c>
       <c r="G16" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H16" t="s">
         <v>216</v>
@@ -4929,10 +5175,10 @@
         <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>371</v>
+        <v>453</v>
       </c>
       <c r="D17" t="s">
-        <v>372</v>
+        <v>454</v>
       </c>
       <c r="E17" t="s">
         <v>25</v>
@@ -4941,7 +5187,7 @@
         <v>35</v>
       </c>
       <c r="G17" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H17" t="s">
         <v>216</v>
@@ -4952,10 +5198,10 @@
         <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>373</v>
+        <v>455</v>
       </c>
       <c r="D18" t="s">
-        <v>374</v>
+        <v>456</v>
       </c>
       <c r="E18" t="s">
         <v>25</v>
@@ -4964,7 +5210,7 @@
         <v>35</v>
       </c>
       <c r="G18" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H18" t="s">
         <v>216</v>
@@ -4975,10 +5221,10 @@
         <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>375</v>
+        <v>457</v>
       </c>
       <c r="D19" t="s">
-        <v>376</v>
+        <v>458</v>
       </c>
       <c r="E19" t="s">
         <v>25</v>
@@ -4987,7 +5233,7 @@
         <v>35</v>
       </c>
       <c r="G19" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H19" t="s">
         <v>216</v>
@@ -4998,10 +5244,10 @@
         <v>17</v>
       </c>
       <c r="C20" t="s">
-        <v>377</v>
+        <v>459</v>
       </c>
       <c r="D20" t="s">
-        <v>378</v>
+        <v>460</v>
       </c>
       <c r="E20" t="s">
         <v>25</v>
@@ -5010,7 +5256,7 @@
         <v>35</v>
       </c>
       <c r="G20" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H20" t="s">
         <v>216</v>
@@ -5021,10 +5267,10 @@
         <v>17</v>
       </c>
       <c r="C21" t="s">
-        <v>379</v>
+        <v>461</v>
       </c>
       <c r="D21" t="s">
-        <v>380</v>
+        <v>462</v>
       </c>
       <c r="E21" t="s">
         <v>25</v>
@@ -5033,7 +5279,7 @@
         <v>35</v>
       </c>
       <c r="G21" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H21" t="s">
         <v>216</v>
@@ -5044,10 +5290,10 @@
         <v>17</v>
       </c>
       <c r="C22" t="s">
-        <v>381</v>
+        <v>463</v>
       </c>
       <c r="D22" t="s">
-        <v>382</v>
+        <v>464</v>
       </c>
       <c r="E22" t="s">
         <v>25</v>
@@ -5056,7 +5302,7 @@
         <v>35</v>
       </c>
       <c r="G22" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H22" t="s">
         <v>216</v>
@@ -5067,10 +5313,10 @@
         <v>17</v>
       </c>
       <c r="C23" t="s">
-        <v>383</v>
+        <v>465</v>
       </c>
       <c r="D23" t="s">
-        <v>384</v>
+        <v>466</v>
       </c>
       <c r="E23" t="s">
         <v>25</v>
@@ -5079,7 +5325,7 @@
         <v>35</v>
       </c>
       <c r="G23" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H23" t="s">
         <v>216</v>
@@ -5090,10 +5336,10 @@
         <v>17</v>
       </c>
       <c r="C24" t="s">
-        <v>385</v>
+        <v>467</v>
       </c>
       <c r="D24" t="s">
-        <v>386</v>
+        <v>468</v>
       </c>
       <c r="E24" t="s">
         <v>25</v>
@@ -5102,7 +5348,7 @@
         <v>35</v>
       </c>
       <c r="G24" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H24" t="s">
         <v>216</v>
@@ -5113,10 +5359,10 @@
         <v>17</v>
       </c>
       <c r="C25" t="s">
-        <v>387</v>
+        <v>469</v>
       </c>
       <c r="D25" t="s">
-        <v>388</v>
+        <v>470</v>
       </c>
       <c r="E25" t="s">
         <v>25</v>
@@ -5125,7 +5371,7 @@
         <v>35</v>
       </c>
       <c r="G25" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H25" t="s">
         <v>216</v>
@@ -5136,10 +5382,10 @@
         <v>17</v>
       </c>
       <c r="C26" t="s">
-        <v>389</v>
+        <v>471</v>
       </c>
       <c r="D26" t="s">
-        <v>390</v>
+        <v>472</v>
       </c>
       <c r="E26" t="s">
         <v>25</v>
@@ -5148,7 +5394,7 @@
         <v>35</v>
       </c>
       <c r="G26" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H26" t="s">
         <v>216</v>
@@ -5159,10 +5405,10 @@
         <v>17</v>
       </c>
       <c r="C27" t="s">
-        <v>391</v>
+        <v>473</v>
       </c>
       <c r="D27" t="s">
-        <v>392</v>
+        <v>474</v>
       </c>
       <c r="E27" t="s">
         <v>25</v>
@@ -5171,7 +5417,7 @@
         <v>35</v>
       </c>
       <c r="G27" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H27" t="s">
         <v>216</v>
@@ -5182,10 +5428,10 @@
         <v>17</v>
       </c>
       <c r="C28" t="s">
-        <v>393</v>
+        <v>475</v>
       </c>
       <c r="D28" t="s">
-        <v>394</v>
+        <v>476</v>
       </c>
       <c r="E28" t="s">
         <v>25</v>
@@ -5194,7 +5440,7 @@
         <v>35</v>
       </c>
       <c r="G28" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H28" t="s">
         <v>216</v>
@@ -5205,10 +5451,10 @@
         <v>17</v>
       </c>
       <c r="C29" t="s">
-        <v>395</v>
+        <v>477</v>
       </c>
       <c r="D29" t="s">
-        <v>396</v>
+        <v>478</v>
       </c>
       <c r="E29" t="s">
         <v>25</v>
@@ -5217,7 +5463,7 @@
         <v>35</v>
       </c>
       <c r="G29" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H29" t="s">
         <v>216</v>
@@ -5228,10 +5474,10 @@
         <v>17</v>
       </c>
       <c r="C30" t="s">
-        <v>397</v>
+        <v>479</v>
       </c>
       <c r="D30" t="s">
-        <v>398</v>
+        <v>480</v>
       </c>
       <c r="E30" t="s">
         <v>25</v>
@@ -5240,7 +5486,7 @@
         <v>35</v>
       </c>
       <c r="G30" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H30" t="s">
         <v>216</v>
@@ -5251,10 +5497,10 @@
         <v>17</v>
       </c>
       <c r="C31" t="s">
-        <v>399</v>
+        <v>481</v>
       </c>
       <c r="D31" t="s">
-        <v>400</v>
+        <v>482</v>
       </c>
       <c r="E31" t="s">
         <v>25</v>
@@ -5263,7 +5509,7 @@
         <v>35</v>
       </c>
       <c r="G31" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H31" t="s">
         <v>216</v>
@@ -5274,10 +5520,10 @@
         <v>17</v>
       </c>
       <c r="C32" t="s">
-        <v>401</v>
+        <v>483</v>
       </c>
       <c r="D32" t="s">
-        <v>402</v>
+        <v>484</v>
       </c>
       <c r="E32" t="s">
         <v>25</v>
@@ -5286,7 +5532,7 @@
         <v>35</v>
       </c>
       <c r="G32" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H32" t="s">
         <v>216</v>
@@ -5297,10 +5543,10 @@
         <v>17</v>
       </c>
       <c r="C33" t="s">
-        <v>403</v>
+        <v>485</v>
       </c>
       <c r="D33" t="s">
-        <v>404</v>
+        <v>486</v>
       </c>
       <c r="E33" t="s">
         <v>25</v>
@@ -5309,7 +5555,7 @@
         <v>35</v>
       </c>
       <c r="G33" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H33" t="s">
         <v>216</v>
@@ -5320,10 +5566,10 @@
         <v>17</v>
       </c>
       <c r="C34" t="s">
-        <v>405</v>
+        <v>487</v>
       </c>
       <c r="D34" t="s">
-        <v>406</v>
+        <v>488</v>
       </c>
       <c r="E34" t="s">
         <v>25</v>
@@ -5332,7 +5578,7 @@
         <v>35</v>
       </c>
       <c r="G34" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H34" t="s">
         <v>216</v>
@@ -5343,10 +5589,10 @@
         <v>17</v>
       </c>
       <c r="C35" t="s">
-        <v>407</v>
+        <v>489</v>
       </c>
       <c r="D35" t="s">
-        <v>408</v>
+        <v>490</v>
       </c>
       <c r="E35" t="s">
         <v>25</v>
@@ -5355,7 +5601,7 @@
         <v>35</v>
       </c>
       <c r="G35" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H35" t="s">
         <v>216</v>
@@ -5366,10 +5612,10 @@
         <v>17</v>
       </c>
       <c r="C36" t="s">
-        <v>409</v>
+        <v>491</v>
       </c>
       <c r="D36" t="s">
-        <v>410</v>
+        <v>492</v>
       </c>
       <c r="E36" t="s">
         <v>25</v>
@@ -5378,7 +5624,7 @@
         <v>35</v>
       </c>
       <c r="G36" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H36" t="s">
         <v>216</v>
@@ -5389,10 +5635,10 @@
         <v>17</v>
       </c>
       <c r="C37" t="s">
-        <v>411</v>
+        <v>493</v>
       </c>
       <c r="D37" t="s">
-        <v>412</v>
+        <v>494</v>
       </c>
       <c r="E37" t="s">
         <v>25</v>
@@ -5401,7 +5647,7 @@
         <v>35</v>
       </c>
       <c r="G37" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H37" t="s">
         <v>216</v>
@@ -5412,10 +5658,10 @@
         <v>17</v>
       </c>
       <c r="C38" t="s">
-        <v>413</v>
+        <v>495</v>
       </c>
       <c r="D38" t="s">
-        <v>414</v>
+        <v>496</v>
       </c>
       <c r="E38" t="s">
         <v>25</v>
@@ -5424,7 +5670,7 @@
         <v>35</v>
       </c>
       <c r="G38" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H38" t="s">
         <v>216</v>
@@ -5435,10 +5681,10 @@
         <v>17</v>
       </c>
       <c r="C39" t="s">
-        <v>415</v>
+        <v>497</v>
       </c>
       <c r="D39" t="s">
-        <v>416</v>
+        <v>498</v>
       </c>
       <c r="E39" t="s">
         <v>25</v>
@@ -5447,7 +5693,7 @@
         <v>35</v>
       </c>
       <c r="G39" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H39" t="s">
         <v>216</v>
@@ -5458,10 +5704,10 @@
         <v>17</v>
       </c>
       <c r="C40" t="s">
-        <v>417</v>
+        <v>499</v>
       </c>
       <c r="D40" t="s">
-        <v>418</v>
+        <v>500</v>
       </c>
       <c r="E40" t="s">
         <v>25</v>
@@ -5470,7 +5716,7 @@
         <v>35</v>
       </c>
       <c r="G40" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H40" t="s">
         <v>216</v>
@@ -5481,10 +5727,10 @@
         <v>17</v>
       </c>
       <c r="C41" t="s">
-        <v>419</v>
+        <v>501</v>
       </c>
       <c r="D41" t="s">
-        <v>420</v>
+        <v>502</v>
       </c>
       <c r="E41" t="s">
         <v>25</v>
@@ -5493,7 +5739,7 @@
         <v>35</v>
       </c>
       <c r="G41" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H41" t="s">
         <v>216</v>
@@ -5504,10 +5750,10 @@
         <v>17</v>
       </c>
       <c r="C42" t="s">
-        <v>421</v>
+        <v>503</v>
       </c>
       <c r="D42" t="s">
-        <v>422</v>
+        <v>504</v>
       </c>
       <c r="E42" t="s">
         <v>25</v>
@@ -5516,7 +5762,7 @@
         <v>35</v>
       </c>
       <c r="G42" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H42" t="s">
         <v>216</v>
@@ -5527,10 +5773,10 @@
         <v>17</v>
       </c>
       <c r="C43" t="s">
-        <v>423</v>
+        <v>505</v>
       </c>
       <c r="D43" t="s">
-        <v>424</v>
+        <v>506</v>
       </c>
       <c r="E43" t="s">
         <v>25</v>
@@ -5539,7 +5785,7 @@
         <v>35</v>
       </c>
       <c r="G43" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H43" t="s">
         <v>216</v>
@@ -5550,10 +5796,10 @@
         <v>17</v>
       </c>
       <c r="C44" t="s">
-        <v>425</v>
+        <v>507</v>
       </c>
       <c r="D44" t="s">
-        <v>426</v>
+        <v>508</v>
       </c>
       <c r="E44" t="s">
         <v>25</v>
@@ -5562,7 +5808,7 @@
         <v>35</v>
       </c>
       <c r="G44" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H44" t="s">
         <v>216</v>
@@ -5573,10 +5819,10 @@
         <v>17</v>
       </c>
       <c r="C45" t="s">
-        <v>427</v>
+        <v>509</v>
       </c>
       <c r="D45" t="s">
-        <v>428</v>
+        <v>510</v>
       </c>
       <c r="E45" t="s">
         <v>25</v>
@@ -5585,7 +5831,7 @@
         <v>35</v>
       </c>
       <c r="G45" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H45" t="s">
         <v>216</v>
@@ -5596,10 +5842,10 @@
         <v>17</v>
       </c>
       <c r="C46" t="s">
-        <v>429</v>
+        <v>511</v>
       </c>
       <c r="D46" t="s">
-        <v>430</v>
+        <v>512</v>
       </c>
       <c r="E46" t="s">
         <v>25</v>
@@ -5608,7 +5854,7 @@
         <v>35</v>
       </c>
       <c r="G46" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H46" t="s">
         <v>216</v>
@@ -5619,10 +5865,10 @@
         <v>17</v>
       </c>
       <c r="C47" t="s">
-        <v>431</v>
+        <v>513</v>
       </c>
       <c r="D47" t="s">
-        <v>432</v>
+        <v>514</v>
       </c>
       <c r="E47" t="s">
         <v>25</v>
@@ -5631,7 +5877,7 @@
         <v>35</v>
       </c>
       <c r="G47" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H47" t="s">
         <v>216</v>
@@ -5642,10 +5888,10 @@
         <v>17</v>
       </c>
       <c r="C48" t="s">
-        <v>433</v>
+        <v>515</v>
       </c>
       <c r="D48" t="s">
-        <v>434</v>
+        <v>516</v>
       </c>
       <c r="E48" t="s">
         <v>25</v>
@@ -5654,7 +5900,7 @@
         <v>35</v>
       </c>
       <c r="G48" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H48" t="s">
         <v>216</v>
@@ -5665,10 +5911,10 @@
         <v>17</v>
       </c>
       <c r="C49" t="s">
-        <v>435</v>
+        <v>517</v>
       </c>
       <c r="D49" t="s">
-        <v>436</v>
+        <v>518</v>
       </c>
       <c r="E49" t="s">
         <v>25</v>
@@ -5677,7 +5923,7 @@
         <v>35</v>
       </c>
       <c r="G49" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H49" t="s">
         <v>216</v>
@@ -5688,10 +5934,10 @@
         <v>17</v>
       </c>
       <c r="C50" t="s">
-        <v>437</v>
+        <v>519</v>
       </c>
       <c r="D50" t="s">
-        <v>438</v>
+        <v>520</v>
       </c>
       <c r="E50" t="s">
         <v>25</v>
@@ -5700,7 +5946,7 @@
         <v>35</v>
       </c>
       <c r="G50" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H50" t="s">
         <v>216</v>
@@ -5711,10 +5957,10 @@
         <v>17</v>
       </c>
       <c r="C51" t="s">
-        <v>439</v>
+        <v>521</v>
       </c>
       <c r="D51" t="s">
-        <v>440</v>
+        <v>522</v>
       </c>
       <c r="E51" t="s">
         <v>25</v>
@@ -5723,7 +5969,7 @@
         <v>35</v>
       </c>
       <c r="G51" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H51" t="s">
         <v>216</v>
@@ -5734,10 +5980,10 @@
         <v>17</v>
       </c>
       <c r="C52" t="s">
-        <v>441</v>
+        <v>523</v>
       </c>
       <c r="D52" t="s">
-        <v>442</v>
+        <v>524</v>
       </c>
       <c r="E52" t="s">
         <v>25</v>
@@ -5746,7 +5992,7 @@
         <v>35</v>
       </c>
       <c r="G52" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H52" t="s">
         <v>216</v>
@@ -5757,10 +6003,10 @@
         <v>17</v>
       </c>
       <c r="C53" t="s">
-        <v>443</v>
+        <v>525</v>
       </c>
       <c r="D53" t="s">
-        <v>444</v>
+        <v>526</v>
       </c>
       <c r="E53" t="s">
         <v>25</v>
@@ -5769,7 +6015,7 @@
         <v>35</v>
       </c>
       <c r="G53" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H53" t="s">
         <v>216</v>
@@ -5780,10 +6026,10 @@
         <v>17</v>
       </c>
       <c r="C54" t="s">
-        <v>445</v>
+        <v>527</v>
       </c>
       <c r="D54" t="s">
-        <v>446</v>
+        <v>528</v>
       </c>
       <c r="E54" t="s">
         <v>25</v>
@@ -5792,7 +6038,7 @@
         <v>35</v>
       </c>
       <c r="G54" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H54" t="s">
         <v>216</v>
@@ -5803,10 +6049,10 @@
         <v>17</v>
       </c>
       <c r="C55" t="s">
-        <v>447</v>
+        <v>529</v>
       </c>
       <c r="D55" t="s">
-        <v>448</v>
+        <v>530</v>
       </c>
       <c r="E55" t="s">
         <v>25</v>
@@ -5815,7 +6061,7 @@
         <v>35</v>
       </c>
       <c r="G55" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H55" t="s">
         <v>216</v>
@@ -5826,10 +6072,10 @@
         <v>17</v>
       </c>
       <c r="C56" t="s">
-        <v>449</v>
+        <v>531</v>
       </c>
       <c r="D56" t="s">
-        <v>450</v>
+        <v>532</v>
       </c>
       <c r="E56" t="s">
         <v>25</v>
@@ -5838,7 +6084,7 @@
         <v>35</v>
       </c>
       <c r="G56" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H56" t="s">
         <v>216</v>
@@ -5849,10 +6095,10 @@
         <v>17</v>
       </c>
       <c r="C57" t="s">
-        <v>451</v>
+        <v>533</v>
       </c>
       <c r="D57" t="s">
-        <v>452</v>
+        <v>534</v>
       </c>
       <c r="E57" t="s">
         <v>25</v>
@@ -5861,7 +6107,7 @@
         <v>35</v>
       </c>
       <c r="G57" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H57" t="s">
         <v>216</v>
@@ -5872,10 +6118,10 @@
         <v>17</v>
       </c>
       <c r="C58" t="s">
-        <v>453</v>
+        <v>535</v>
       </c>
       <c r="D58" t="s">
-        <v>454</v>
+        <v>536</v>
       </c>
       <c r="E58" t="s">
         <v>25</v>
@@ -5884,7 +6130,7 @@
         <v>35</v>
       </c>
       <c r="G58" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H58" t="s">
         <v>216</v>
@@ -5895,10 +6141,10 @@
         <v>17</v>
       </c>
       <c r="C59" t="s">
-        <v>455</v>
+        <v>537</v>
       </c>
       <c r="D59" t="s">
-        <v>456</v>
+        <v>538</v>
       </c>
       <c r="E59" t="s">
         <v>25</v>
@@ -5907,7 +6153,7 @@
         <v>35</v>
       </c>
       <c r="G59" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H59" t="s">
         <v>216</v>
@@ -5918,10 +6164,10 @@
         <v>17</v>
       </c>
       <c r="C60" t="s">
-        <v>457</v>
+        <v>539</v>
       </c>
       <c r="D60" t="s">
-        <v>458</v>
+        <v>540</v>
       </c>
       <c r="E60" t="s">
         <v>25</v>
@@ -5930,7 +6176,7 @@
         <v>35</v>
       </c>
       <c r="G60" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H60" t="s">
         <v>216</v>
@@ -5941,10 +6187,10 @@
         <v>17</v>
       </c>
       <c r="C61" t="s">
-        <v>459</v>
+        <v>541</v>
       </c>
       <c r="D61" t="s">
-        <v>460</v>
+        <v>542</v>
       </c>
       <c r="E61" t="s">
         <v>25</v>
@@ -5953,7 +6199,7 @@
         <v>35</v>
       </c>
       <c r="G61" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H61" t="s">
         <v>216</v>
@@ -5964,10 +6210,10 @@
         <v>17</v>
       </c>
       <c r="C62" t="s">
-        <v>461</v>
+        <v>543</v>
       </c>
       <c r="D62" t="s">
-        <v>462</v>
+        <v>544</v>
       </c>
       <c r="E62" t="s">
         <v>25</v>
@@ -5976,7 +6222,7 @@
         <v>35</v>
       </c>
       <c r="G62" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H62" t="s">
         <v>216</v>
@@ -5987,10 +6233,10 @@
         <v>17</v>
       </c>
       <c r="C63" t="s">
-        <v>463</v>
+        <v>545</v>
       </c>
       <c r="D63" t="s">
-        <v>464</v>
+        <v>546</v>
       </c>
       <c r="E63" t="s">
         <v>25</v>
@@ -5999,7 +6245,7 @@
         <v>35</v>
       </c>
       <c r="G63" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H63" t="s">
         <v>216</v>
@@ -6010,10 +6256,10 @@
         <v>17</v>
       </c>
       <c r="C64" t="s">
-        <v>465</v>
+        <v>547</v>
       </c>
       <c r="D64" t="s">
-        <v>466</v>
+        <v>548</v>
       </c>
       <c r="E64" t="s">
         <v>25</v>
@@ -6022,7 +6268,7 @@
         <v>35</v>
       </c>
       <c r="G64" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H64" t="s">
         <v>216</v>
@@ -6033,10 +6279,10 @@
         <v>17</v>
       </c>
       <c r="C65" t="s">
-        <v>467</v>
+        <v>549</v>
       </c>
       <c r="D65" t="s">
-        <v>468</v>
+        <v>550</v>
       </c>
       <c r="E65" t="s">
         <v>25</v>
@@ -6045,7 +6291,7 @@
         <v>35</v>
       </c>
       <c r="G65" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H65" t="s">
         <v>216</v>
@@ -6056,10 +6302,10 @@
         <v>17</v>
       </c>
       <c r="C66" t="s">
-        <v>469</v>
+        <v>551</v>
       </c>
       <c r="D66" t="s">
-        <v>470</v>
+        <v>552</v>
       </c>
       <c r="E66" t="s">
         <v>25</v>
@@ -6068,7 +6314,7 @@
         <v>35</v>
       </c>
       <c r="G66" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H66" t="s">
         <v>216</v>
@@ -6079,10 +6325,10 @@
         <v>17</v>
       </c>
       <c r="C67" t="s">
-        <v>471</v>
+        <v>553</v>
       </c>
       <c r="D67" t="s">
-        <v>472</v>
+        <v>554</v>
       </c>
       <c r="E67" t="s">
         <v>25</v>
@@ -6091,7 +6337,7 @@
         <v>35</v>
       </c>
       <c r="G67" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H67" t="s">
         <v>216</v>
@@ -6102,10 +6348,10 @@
         <v>17</v>
       </c>
       <c r="C68" t="s">
-        <v>473</v>
+        <v>555</v>
       </c>
       <c r="D68" t="s">
-        <v>474</v>
+        <v>556</v>
       </c>
       <c r="E68" t="s">
         <v>25</v>
@@ -6114,7 +6360,7 @@
         <v>35</v>
       </c>
       <c r="G68" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H68" t="s">
         <v>216</v>
@@ -6125,10 +6371,10 @@
         <v>17</v>
       </c>
       <c r="C69" t="s">
-        <v>475</v>
+        <v>557</v>
       </c>
       <c r="D69" t="s">
-        <v>476</v>
+        <v>558</v>
       </c>
       <c r="E69" t="s">
         <v>25</v>
@@ -6137,7 +6383,7 @@
         <v>35</v>
       </c>
       <c r="G69" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H69" t="s">
         <v>216</v>
@@ -6148,10 +6394,10 @@
         <v>17</v>
       </c>
       <c r="C70" t="s">
-        <v>477</v>
+        <v>559</v>
       </c>
       <c r="D70" t="s">
-        <v>478</v>
+        <v>560</v>
       </c>
       <c r="E70" t="s">
         <v>25</v>
@@ -6160,7 +6406,7 @@
         <v>35</v>
       </c>
       <c r="G70" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H70" t="s">
         <v>216</v>
@@ -6171,10 +6417,10 @@
         <v>17</v>
       </c>
       <c r="C71" t="s">
-        <v>479</v>
+        <v>561</v>
       </c>
       <c r="D71" t="s">
-        <v>480</v>
+        <v>562</v>
       </c>
       <c r="E71" t="s">
         <v>25</v>
@@ -6183,7 +6429,7 @@
         <v>35</v>
       </c>
       <c r="G71" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H71" t="s">
         <v>216</v>
@@ -6194,10 +6440,10 @@
         <v>17</v>
       </c>
       <c r="C72" t="s">
-        <v>481</v>
+        <v>563</v>
       </c>
       <c r="D72" t="s">
-        <v>482</v>
+        <v>564</v>
       </c>
       <c r="E72" t="s">
         <v>25</v>
@@ -6206,7 +6452,7 @@
         <v>35</v>
       </c>
       <c r="G72" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H72" t="s">
         <v>216</v>
@@ -6217,10 +6463,10 @@
         <v>17</v>
       </c>
       <c r="C73" t="s">
-        <v>483</v>
+        <v>565</v>
       </c>
       <c r="D73" t="s">
-        <v>484</v>
+        <v>566</v>
       </c>
       <c r="E73" t="s">
         <v>25</v>
@@ -6229,7 +6475,7 @@
         <v>35</v>
       </c>
       <c r="G73" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H73" t="s">
         <v>216</v>
@@ -6240,10 +6486,10 @@
         <v>17</v>
       </c>
       <c r="C74" t="s">
-        <v>485</v>
+        <v>567</v>
       </c>
       <c r="D74" t="s">
-        <v>486</v>
+        <v>568</v>
       </c>
       <c r="E74" t="s">
         <v>25</v>
@@ -6252,7 +6498,7 @@
         <v>35</v>
       </c>
       <c r="G74" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H74" t="s">
         <v>216</v>
@@ -6263,10 +6509,10 @@
         <v>17</v>
       </c>
       <c r="C75" t="s">
-        <v>487</v>
+        <v>569</v>
       </c>
       <c r="D75" t="s">
-        <v>488</v>
+        <v>570</v>
       </c>
       <c r="E75" t="s">
         <v>25</v>
@@ -6275,7 +6521,7 @@
         <v>35</v>
       </c>
       <c r="G75" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H75" t="s">
         <v>216</v>
@@ -6286,10 +6532,10 @@
         <v>17</v>
       </c>
       <c r="C76" t="s">
-        <v>489</v>
+        <v>571</v>
       </c>
       <c r="D76" t="s">
-        <v>490</v>
+        <v>572</v>
       </c>
       <c r="E76" t="s">
         <v>25</v>
@@ -6298,7 +6544,7 @@
         <v>35</v>
       </c>
       <c r="G76" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H76" t="s">
         <v>216</v>
@@ -6309,10 +6555,10 @@
         <v>17</v>
       </c>
       <c r="C77" t="s">
-        <v>491</v>
+        <v>573</v>
       </c>
       <c r="D77" t="s">
-        <v>492</v>
+        <v>574</v>
       </c>
       <c r="E77" t="s">
         <v>25</v>
@@ -6321,7 +6567,7 @@
         <v>35</v>
       </c>
       <c r="G77" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H77" t="s">
         <v>216</v>
@@ -6332,10 +6578,10 @@
         <v>17</v>
       </c>
       <c r="C78" t="s">
-        <v>493</v>
+        <v>575</v>
       </c>
       <c r="D78" t="s">
-        <v>494</v>
+        <v>576</v>
       </c>
       <c r="E78" t="s">
         <v>25</v>
@@ -6344,7 +6590,7 @@
         <v>35</v>
       </c>
       <c r="G78" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H78" t="s">
         <v>216</v>
@@ -6355,10 +6601,10 @@
         <v>17</v>
       </c>
       <c r="C79" t="s">
-        <v>495</v>
+        <v>577</v>
       </c>
       <c r="D79" t="s">
-        <v>496</v>
+        <v>578</v>
       </c>
       <c r="E79" t="s">
         <v>25</v>
@@ -6367,7 +6613,7 @@
         <v>35</v>
       </c>
       <c r="G79" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H79" t="s">
         <v>216</v>
@@ -6378,10 +6624,10 @@
         <v>17</v>
       </c>
       <c r="C80" t="s">
-        <v>497</v>
+        <v>579</v>
       </c>
       <c r="D80" t="s">
-        <v>498</v>
+        <v>580</v>
       </c>
       <c r="E80" t="s">
         <v>25</v>
@@ -6390,7 +6636,7 @@
         <v>35</v>
       </c>
       <c r="G80" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H80" t="s">
         <v>216</v>
@@ -6401,10 +6647,10 @@
         <v>17</v>
       </c>
       <c r="C81" t="s">
-        <v>499</v>
+        <v>581</v>
       </c>
       <c r="D81" t="s">
-        <v>500</v>
+        <v>582</v>
       </c>
       <c r="E81" t="s">
         <v>25</v>
@@ -6413,7 +6659,7 @@
         <v>35</v>
       </c>
       <c r="G81" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H81" t="s">
         <v>216</v>
@@ -6424,10 +6670,10 @@
         <v>17</v>
       </c>
       <c r="C82" t="s">
-        <v>501</v>
+        <v>583</v>
       </c>
       <c r="D82" t="s">
-        <v>502</v>
+        <v>584</v>
       </c>
       <c r="E82" t="s">
         <v>25</v>
@@ -6436,7 +6682,7 @@
         <v>35</v>
       </c>
       <c r="G82" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H82" t="s">
         <v>216</v>
@@ -6447,10 +6693,10 @@
         <v>17</v>
       </c>
       <c r="C83" t="s">
-        <v>503</v>
+        <v>585</v>
       </c>
       <c r="D83" t="s">
-        <v>504</v>
+        <v>586</v>
       </c>
       <c r="E83" t="s">
         <v>25</v>
@@ -6459,7 +6705,7 @@
         <v>35</v>
       </c>
       <c r="G83" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H83" t="s">
         <v>216</v>
@@ -6470,10 +6716,10 @@
         <v>17</v>
       </c>
       <c r="C84" t="s">
-        <v>505</v>
+        <v>587</v>
       </c>
       <c r="D84" t="s">
-        <v>506</v>
+        <v>588</v>
       </c>
       <c r="E84" t="s">
         <v>25</v>
@@ -6482,7 +6728,7 @@
         <v>35</v>
       </c>
       <c r="G84" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H84" t="s">
         <v>216</v>
@@ -6493,10 +6739,10 @@
         <v>17</v>
       </c>
       <c r="C85" t="s">
-        <v>507</v>
+        <v>589</v>
       </c>
       <c r="D85" t="s">
-        <v>508</v>
+        <v>590</v>
       </c>
       <c r="E85" t="s">
         <v>25</v>
@@ -6505,7 +6751,7 @@
         <v>35</v>
       </c>
       <c r="G85" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H85" t="s">
         <v>216</v>
@@ -6516,10 +6762,10 @@
         <v>17</v>
       </c>
       <c r="C86" t="s">
-        <v>509</v>
+        <v>591</v>
       </c>
       <c r="D86" t="s">
-        <v>510</v>
+        <v>592</v>
       </c>
       <c r="E86" t="s">
         <v>25</v>
@@ -6528,7 +6774,7 @@
         <v>35</v>
       </c>
       <c r="G86" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H86" t="s">
         <v>216</v>
@@ -6539,10 +6785,10 @@
         <v>17</v>
       </c>
       <c r="C87" t="s">
-        <v>511</v>
+        <v>593</v>
       </c>
       <c r="D87" t="s">
-        <v>512</v>
+        <v>594</v>
       </c>
       <c r="E87" t="s">
         <v>25</v>
@@ -6551,7 +6797,7 @@
         <v>35</v>
       </c>
       <c r="G87" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H87" t="s">
         <v>216</v>
@@ -6562,10 +6808,10 @@
         <v>17</v>
       </c>
       <c r="C88" t="s">
-        <v>513</v>
+        <v>595</v>
       </c>
       <c r="D88" t="s">
-        <v>514</v>
+        <v>596</v>
       </c>
       <c r="E88" t="s">
         <v>25</v>
@@ -6574,7 +6820,7 @@
         <v>35</v>
       </c>
       <c r="G88" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H88" t="s">
         <v>216</v>
@@ -6585,10 +6831,10 @@
         <v>17</v>
       </c>
       <c r="C89" t="s">
-        <v>515</v>
+        <v>597</v>
       </c>
       <c r="D89" t="s">
-        <v>516</v>
+        <v>598</v>
       </c>
       <c r="E89" t="s">
         <v>25</v>
@@ -6597,7 +6843,7 @@
         <v>35</v>
       </c>
       <c r="G89" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H89" t="s">
         <v>216</v>
@@ -6608,10 +6854,10 @@
         <v>17</v>
       </c>
       <c r="C90" t="s">
-        <v>517</v>
+        <v>599</v>
       </c>
       <c r="D90" t="s">
-        <v>518</v>
+        <v>600</v>
       </c>
       <c r="E90" t="s">
         <v>25</v>
@@ -6620,7 +6866,7 @@
         <v>35</v>
       </c>
       <c r="G90" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H90" t="s">
         <v>216</v>
@@ -6631,10 +6877,10 @@
         <v>17</v>
       </c>
       <c r="C91" t="s">
-        <v>519</v>
+        <v>601</v>
       </c>
       <c r="D91" t="s">
-        <v>520</v>
+        <v>602</v>
       </c>
       <c r="E91" t="s">
         <v>25</v>
@@ -6643,7 +6889,7 @@
         <v>35</v>
       </c>
       <c r="G91" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H91" t="s">
         <v>216</v>
@@ -6654,10 +6900,10 @@
         <v>17</v>
       </c>
       <c r="C92" t="s">
-        <v>521</v>
+        <v>603</v>
       </c>
       <c r="D92" t="s">
-        <v>522</v>
+        <v>604</v>
       </c>
       <c r="E92" t="s">
         <v>25</v>
@@ -6666,7 +6912,7 @@
         <v>35</v>
       </c>
       <c r="G92" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H92" t="s">
         <v>216</v>
@@ -6677,10 +6923,10 @@
         <v>17</v>
       </c>
       <c r="C93" t="s">
-        <v>523</v>
+        <v>605</v>
       </c>
       <c r="D93" t="s">
-        <v>524</v>
+        <v>606</v>
       </c>
       <c r="E93" t="s">
         <v>25</v>
@@ -6689,7 +6935,7 @@
         <v>35</v>
       </c>
       <c r="G93" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H93" t="s">
         <v>216</v>
@@ -6700,10 +6946,10 @@
         <v>17</v>
       </c>
       <c r="C94" t="s">
-        <v>525</v>
+        <v>607</v>
       </c>
       <c r="D94" t="s">
-        <v>526</v>
+        <v>608</v>
       </c>
       <c r="E94" t="s">
         <v>25</v>
@@ -6712,7 +6958,7 @@
         <v>35</v>
       </c>
       <c r="G94" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H94" t="s">
         <v>216</v>
@@ -6723,10 +6969,10 @@
         <v>17</v>
       </c>
       <c r="C95" t="s">
-        <v>527</v>
+        <v>609</v>
       </c>
       <c r="D95" t="s">
-        <v>528</v>
+        <v>610</v>
       </c>
       <c r="E95" t="s">
         <v>25</v>
@@ -6735,7 +6981,7 @@
         <v>35</v>
       </c>
       <c r="G95" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H95" t="s">
         <v>216</v>
@@ -6746,10 +6992,10 @@
         <v>17</v>
       </c>
       <c r="C96" t="s">
-        <v>529</v>
+        <v>611</v>
       </c>
       <c r="D96" t="s">
-        <v>530</v>
+        <v>612</v>
       </c>
       <c r="E96" t="s">
         <v>25</v>
@@ -6758,7 +7004,7 @@
         <v>35</v>
       </c>
       <c r="G96" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H96" t="s">
         <v>216</v>
@@ -6769,10 +7015,10 @@
         <v>17</v>
       </c>
       <c r="C97" t="s">
-        <v>531</v>
+        <v>613</v>
       </c>
       <c r="D97" t="s">
-        <v>532</v>
+        <v>614</v>
       </c>
       <c r="E97" t="s">
         <v>25</v>
@@ -6781,7 +7027,7 @@
         <v>35</v>
       </c>
       <c r="G97" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H97" t="s">
         <v>216</v>
@@ -6792,10 +7038,10 @@
         <v>17</v>
       </c>
       <c r="C98" t="s">
-        <v>533</v>
+        <v>615</v>
       </c>
       <c r="D98" t="s">
-        <v>534</v>
+        <v>616</v>
       </c>
       <c r="E98" t="s">
         <v>25</v>
@@ -6804,7 +7050,7 @@
         <v>35</v>
       </c>
       <c r="G98" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H98" t="s">
         <v>216</v>
@@ -6815,10 +7061,10 @@
         <v>17</v>
       </c>
       <c r="C99" t="s">
-        <v>535</v>
+        <v>617</v>
       </c>
       <c r="D99" t="s">
-        <v>536</v>
+        <v>618</v>
       </c>
       <c r="E99" t="s">
         <v>25</v>
@@ -6827,7 +7073,7 @@
         <v>35</v>
       </c>
       <c r="G99" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H99" t="s">
         <v>216</v>
@@ -6838,10 +7084,10 @@
         <v>17</v>
       </c>
       <c r="C100" t="s">
-        <v>537</v>
+        <v>619</v>
       </c>
       <c r="D100" t="s">
-        <v>538</v>
+        <v>620</v>
       </c>
       <c r="E100" t="s">
         <v>25</v>
@@ -6850,7 +7096,7 @@
         <v>35</v>
       </c>
       <c r="G100" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H100" t="s">
         <v>216</v>
@@ -6861,10 +7107,10 @@
         <v>17</v>
       </c>
       <c r="C101" t="s">
-        <v>539</v>
+        <v>621</v>
       </c>
       <c r="D101" t="s">
-        <v>540</v>
+        <v>622</v>
       </c>
       <c r="E101" t="s">
         <v>25</v>
@@ -6873,7 +7119,7 @@
         <v>35</v>
       </c>
       <c r="G101" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H101" t="s">
         <v>216</v>
@@ -6884,10 +7130,10 @@
         <v>17</v>
       </c>
       <c r="C102" t="s">
-        <v>541</v>
+        <v>623</v>
       </c>
       <c r="D102" t="s">
-        <v>542</v>
+        <v>624</v>
       </c>
       <c r="E102" t="s">
         <v>25</v>
@@ -6896,7 +7142,7 @@
         <v>35</v>
       </c>
       <c r="G102" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H102" t="s">
         <v>216</v>
@@ -6907,10 +7153,10 @@
         <v>17</v>
       </c>
       <c r="C103" t="s">
-        <v>543</v>
+        <v>625</v>
       </c>
       <c r="D103" t="s">
-        <v>544</v>
+        <v>626</v>
       </c>
       <c r="E103" t="s">
         <v>25</v>
@@ -6919,7 +7165,7 @@
         <v>35</v>
       </c>
       <c r="G103" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H103" t="s">
         <v>216</v>
@@ -6930,10 +7176,10 @@
         <v>17</v>
       </c>
       <c r="C104" t="s">
-        <v>545</v>
+        <v>627</v>
       </c>
       <c r="D104" t="s">
-        <v>546</v>
+        <v>628</v>
       </c>
       <c r="E104" t="s">
         <v>25</v>
@@ -6942,7 +7188,7 @@
         <v>35</v>
       </c>
       <c r="G104" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H104" t="s">
         <v>216</v>
@@ -6953,10 +7199,10 @@
         <v>17</v>
       </c>
       <c r="C105" t="s">
-        <v>547</v>
+        <v>629</v>
       </c>
       <c r="D105" t="s">
-        <v>548</v>
+        <v>630</v>
       </c>
       <c r="E105" t="s">
         <v>25</v>
@@ -6965,7 +7211,7 @@
         <v>35</v>
       </c>
       <c r="G105" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H105" t="s">
         <v>216</v>
@@ -6976,10 +7222,10 @@
         <v>17</v>
       </c>
       <c r="C106" t="s">
-        <v>549</v>
+        <v>631</v>
       </c>
       <c r="D106" t="s">
-        <v>550</v>
+        <v>632</v>
       </c>
       <c r="E106" t="s">
         <v>25</v>
@@ -6988,7 +7234,7 @@
         <v>35</v>
       </c>
       <c r="G106" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H106" t="s">
         <v>216</v>
@@ -6999,10 +7245,10 @@
         <v>17</v>
       </c>
       <c r="C107" t="s">
-        <v>551</v>
+        <v>633</v>
       </c>
       <c r="D107" t="s">
-        <v>552</v>
+        <v>634</v>
       </c>
       <c r="E107" t="s">
         <v>25</v>
@@ -7011,7 +7257,7 @@
         <v>35</v>
       </c>
       <c r="G107" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H107" t="s">
         <v>216</v>
@@ -7022,10 +7268,10 @@
         <v>17</v>
       </c>
       <c r="C108" t="s">
-        <v>553</v>
+        <v>635</v>
       </c>
       <c r="D108" t="s">
-        <v>554</v>
+        <v>636</v>
       </c>
       <c r="E108" t="s">
         <v>25</v>
@@ -7034,7 +7280,7 @@
         <v>35</v>
       </c>
       <c r="G108" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H108" t="s">
         <v>216</v>
@@ -7045,10 +7291,10 @@
         <v>17</v>
       </c>
       <c r="C109" t="s">
-        <v>555</v>
+        <v>637</v>
       </c>
       <c r="D109" t="s">
-        <v>556</v>
+        <v>638</v>
       </c>
       <c r="E109" t="s">
         <v>25</v>
@@ -7057,7 +7303,7 @@
         <v>35</v>
       </c>
       <c r="G109" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H109" t="s">
         <v>216</v>
@@ -7068,10 +7314,10 @@
         <v>17</v>
       </c>
       <c r="C110" t="s">
-        <v>557</v>
+        <v>639</v>
       </c>
       <c r="D110" t="s">
-        <v>558</v>
+        <v>640</v>
       </c>
       <c r="E110" t="s">
         <v>25</v>
@@ -7080,7 +7326,7 @@
         <v>35</v>
       </c>
       <c r="G110" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H110" t="s">
         <v>216</v>
@@ -7091,10 +7337,10 @@
         <v>17</v>
       </c>
       <c r="C111" t="s">
-        <v>559</v>
+        <v>641</v>
       </c>
       <c r="D111" t="s">
-        <v>560</v>
+        <v>642</v>
       </c>
       <c r="E111" t="s">
         <v>25</v>
@@ -7103,7 +7349,7 @@
         <v>35</v>
       </c>
       <c r="G111" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H111" t="s">
         <v>216</v>
@@ -7114,10 +7360,10 @@
         <v>17</v>
       </c>
       <c r="C112" t="s">
-        <v>561</v>
+        <v>643</v>
       </c>
       <c r="D112" t="s">
-        <v>562</v>
+        <v>644</v>
       </c>
       <c r="E112" t="s">
         <v>25</v>
@@ -7126,7 +7372,7 @@
         <v>35</v>
       </c>
       <c r="G112" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H112" t="s">
         <v>216</v>
@@ -7137,10 +7383,10 @@
         <v>17</v>
       </c>
       <c r="C113" t="s">
-        <v>563</v>
+        <v>645</v>
       </c>
       <c r="D113" t="s">
-        <v>564</v>
+        <v>646</v>
       </c>
       <c r="E113" t="s">
         <v>25</v>
@@ -7149,7 +7395,7 @@
         <v>35</v>
       </c>
       <c r="G113" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H113" t="s">
         <v>216</v>
@@ -7160,10 +7406,10 @@
         <v>17</v>
       </c>
       <c r="C114" t="s">
-        <v>565</v>
+        <v>647</v>
       </c>
       <c r="D114" t="s">
-        <v>566</v>
+        <v>648</v>
       </c>
       <c r="E114" t="s">
         <v>25</v>
@@ -7172,7 +7418,7 @@
         <v>35</v>
       </c>
       <c r="G114" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H114" t="s">
         <v>216</v>
@@ -7183,10 +7429,10 @@
         <v>17</v>
       </c>
       <c r="C115" t="s">
-        <v>567</v>
+        <v>649</v>
       </c>
       <c r="D115" t="s">
-        <v>568</v>
+        <v>650</v>
       </c>
       <c r="E115" t="s">
         <v>25</v>
@@ -7195,7 +7441,7 @@
         <v>35</v>
       </c>
       <c r="G115" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H115" t="s">
         <v>216</v>
@@ -7206,10 +7452,10 @@
         <v>17</v>
       </c>
       <c r="C116" t="s">
-        <v>569</v>
+        <v>651</v>
       </c>
       <c r="D116" t="s">
-        <v>570</v>
+        <v>652</v>
       </c>
       <c r="E116" t="s">
         <v>25</v>
@@ -7218,7 +7464,7 @@
         <v>35</v>
       </c>
       <c r="G116" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H116" t="s">
         <v>216</v>
@@ -7229,10 +7475,10 @@
         <v>17</v>
       </c>
       <c r="C117" t="s">
-        <v>571</v>
+        <v>653</v>
       </c>
       <c r="D117" t="s">
-        <v>572</v>
+        <v>654</v>
       </c>
       <c r="E117" t="s">
         <v>25</v>
@@ -7241,7 +7487,7 @@
         <v>35</v>
       </c>
       <c r="G117" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H117" t="s">
         <v>216</v>
@@ -7252,10 +7498,10 @@
         <v>17</v>
       </c>
       <c r="C118" t="s">
-        <v>573</v>
+        <v>655</v>
       </c>
       <c r="D118" t="s">
-        <v>574</v>
+        <v>656</v>
       </c>
       <c r="E118" t="s">
         <v>25</v>
@@ -7264,7 +7510,7 @@
         <v>35</v>
       </c>
       <c r="G118" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H118" t="s">
         <v>216</v>
@@ -7275,10 +7521,10 @@
         <v>17</v>
       </c>
       <c r="C119" t="s">
-        <v>575</v>
+        <v>657</v>
       </c>
       <c r="D119" t="s">
-        <v>576</v>
+        <v>658</v>
       </c>
       <c r="E119" t="s">
         <v>25</v>
@@ -7287,7 +7533,7 @@
         <v>35</v>
       </c>
       <c r="G119" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H119" t="s">
         <v>216</v>
@@ -7298,10 +7544,10 @@
         <v>17</v>
       </c>
       <c r="C120" t="s">
-        <v>577</v>
+        <v>659</v>
       </c>
       <c r="D120" t="s">
-        <v>578</v>
+        <v>660</v>
       </c>
       <c r="E120" t="s">
         <v>25</v>
@@ -7310,7 +7556,7 @@
         <v>35</v>
       </c>
       <c r="G120" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H120" t="s">
         <v>216</v>
@@ -7321,10 +7567,10 @@
         <v>17</v>
       </c>
       <c r="C121" t="s">
-        <v>579</v>
+        <v>661</v>
       </c>
       <c r="D121" t="s">
-        <v>580</v>
+        <v>662</v>
       </c>
       <c r="E121" t="s">
         <v>25</v>
@@ -7333,7 +7579,7 @@
         <v>35</v>
       </c>
       <c r="G121" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H121" t="s">
         <v>216</v>
@@ -7344,10 +7590,10 @@
         <v>17</v>
       </c>
       <c r="C122" t="s">
-        <v>581</v>
+        <v>663</v>
       </c>
       <c r="D122" t="s">
-        <v>582</v>
+        <v>664</v>
       </c>
       <c r="E122" t="s">
         <v>25</v>
@@ -7356,7 +7602,7 @@
         <v>35</v>
       </c>
       <c r="G122" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H122" t="s">
         <v>216</v>
@@ -7367,10 +7613,10 @@
         <v>17</v>
       </c>
       <c r="C123" t="s">
-        <v>583</v>
+        <v>665</v>
       </c>
       <c r="D123" t="s">
-        <v>584</v>
+        <v>666</v>
       </c>
       <c r="E123" t="s">
         <v>25</v>
@@ -7379,7 +7625,7 @@
         <v>35</v>
       </c>
       <c r="G123" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H123" t="s">
         <v>216</v>
@@ -7390,10 +7636,10 @@
         <v>17</v>
       </c>
       <c r="C124" t="s">
-        <v>585</v>
+        <v>667</v>
       </c>
       <c r="D124" t="s">
-        <v>586</v>
+        <v>668</v>
       </c>
       <c r="E124" t="s">
         <v>25</v>
@@ -7402,7 +7648,7 @@
         <v>35</v>
       </c>
       <c r="G124" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H124" t="s">
         <v>216</v>
@@ -7413,10 +7659,10 @@
         <v>17</v>
       </c>
       <c r="C125" t="s">
-        <v>587</v>
+        <v>669</v>
       </c>
       <c r="D125" t="s">
-        <v>588</v>
+        <v>670</v>
       </c>
       <c r="E125" t="s">
         <v>25</v>
@@ -7425,7 +7671,7 @@
         <v>35</v>
       </c>
       <c r="G125" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H125" t="s">
         <v>216</v>
@@ -7436,10 +7682,10 @@
         <v>17</v>
       </c>
       <c r="C126" t="s">
-        <v>589</v>
+        <v>671</v>
       </c>
       <c r="D126" t="s">
-        <v>590</v>
+        <v>672</v>
       </c>
       <c r="E126" t="s">
         <v>25</v>
@@ -7448,7 +7694,7 @@
         <v>35</v>
       </c>
       <c r="G126" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H126" t="s">
         <v>216</v>
@@ -7459,10 +7705,10 @@
         <v>17</v>
       </c>
       <c r="C127" t="s">
-        <v>591</v>
+        <v>673</v>
       </c>
       <c r="D127" t="s">
-        <v>592</v>
+        <v>674</v>
       </c>
       <c r="E127" t="s">
         <v>25</v>
@@ -7471,7 +7717,7 @@
         <v>35</v>
       </c>
       <c r="G127" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H127" t="s">
         <v>216</v>
@@ -7482,10 +7728,10 @@
         <v>17</v>
       </c>
       <c r="C128" t="s">
-        <v>593</v>
+        <v>675</v>
       </c>
       <c r="D128" t="s">
-        <v>594</v>
+        <v>676</v>
       </c>
       <c r="E128" t="s">
         <v>25</v>
@@ -7494,7 +7740,7 @@
         <v>35</v>
       </c>
       <c r="G128" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H128" t="s">
         <v>216</v>
@@ -7505,10 +7751,10 @@
         <v>17</v>
       </c>
       <c r="C129" t="s">
-        <v>595</v>
+        <v>677</v>
       </c>
       <c r="D129" t="s">
-        <v>596</v>
+        <v>678</v>
       </c>
       <c r="E129" t="s">
         <v>25</v>
@@ -7517,7 +7763,7 @@
         <v>35</v>
       </c>
       <c r="G129" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H129" t="s">
         <v>216</v>
@@ -7528,10 +7774,10 @@
         <v>17</v>
       </c>
       <c r="C130" t="s">
-        <v>597</v>
+        <v>679</v>
       </c>
       <c r="D130" t="s">
-        <v>598</v>
+        <v>680</v>
       </c>
       <c r="E130" t="s">
         <v>25</v>
@@ -7540,7 +7786,7 @@
         <v>35</v>
       </c>
       <c r="G130" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H130" t="s">
         <v>216</v>
@@ -7551,10 +7797,10 @@
         <v>17</v>
       </c>
       <c r="C131" t="s">
-        <v>599</v>
+        <v>681</v>
       </c>
       <c r="D131" t="s">
-        <v>600</v>
+        <v>682</v>
       </c>
       <c r="E131" t="s">
         <v>25</v>
@@ -7563,7 +7809,7 @@
         <v>35</v>
       </c>
       <c r="G131" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H131" t="s">
         <v>216</v>
@@ -7574,10 +7820,10 @@
         <v>17</v>
       </c>
       <c r="C132" t="s">
-        <v>601</v>
+        <v>683</v>
       </c>
       <c r="D132" t="s">
-        <v>602</v>
+        <v>684</v>
       </c>
       <c r="E132" t="s">
         <v>25</v>
@@ -7586,7 +7832,7 @@
         <v>35</v>
       </c>
       <c r="G132" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H132" t="s">
         <v>216</v>
@@ -7597,10 +7843,10 @@
         <v>17</v>
       </c>
       <c r="C133" t="s">
-        <v>603</v>
+        <v>685</v>
       </c>
       <c r="D133" t="s">
-        <v>604</v>
+        <v>686</v>
       </c>
       <c r="E133" t="s">
         <v>25</v>
@@ -7609,7 +7855,7 @@
         <v>35</v>
       </c>
       <c r="G133" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H133" t="s">
         <v>216</v>
@@ -7620,10 +7866,10 @@
         <v>17</v>
       </c>
       <c r="C134" t="s">
-        <v>605</v>
+        <v>687</v>
       </c>
       <c r="D134" t="s">
-        <v>606</v>
+        <v>688</v>
       </c>
       <c r="E134" t="s">
         <v>25</v>
@@ -7632,7 +7878,7 @@
         <v>35</v>
       </c>
       <c r="G134" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H134" t="s">
         <v>216</v>
@@ -7643,10 +7889,10 @@
         <v>17</v>
       </c>
       <c r="C135" t="s">
-        <v>607</v>
+        <v>689</v>
       </c>
       <c r="D135" t="s">
-        <v>608</v>
+        <v>690</v>
       </c>
       <c r="E135" t="s">
         <v>25</v>
@@ -7655,7 +7901,7 @@
         <v>35</v>
       </c>
       <c r="G135" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H135" t="s">
         <v>216</v>
@@ -7666,10 +7912,10 @@
         <v>17</v>
       </c>
       <c r="C136" t="s">
-        <v>609</v>
+        <v>691</v>
       </c>
       <c r="D136" t="s">
-        <v>610</v>
+        <v>692</v>
       </c>
       <c r="E136" t="s">
         <v>25</v>
@@ -7678,7 +7924,7 @@
         <v>35</v>
       </c>
       <c r="G136" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H136" t="s">
         <v>216</v>
@@ -7689,10 +7935,10 @@
         <v>17</v>
       </c>
       <c r="C137" t="s">
-        <v>611</v>
+        <v>693</v>
       </c>
       <c r="D137" t="s">
-        <v>612</v>
+        <v>694</v>
       </c>
       <c r="E137" t="s">
         <v>25</v>
@@ -7701,7 +7947,7 @@
         <v>35</v>
       </c>
       <c r="G137" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H137" t="s">
         <v>216</v>
@@ -7712,10 +7958,10 @@
         <v>17</v>
       </c>
       <c r="C138" t="s">
-        <v>613</v>
+        <v>695</v>
       </c>
       <c r="D138" t="s">
-        <v>614</v>
+        <v>696</v>
       </c>
       <c r="E138" t="s">
         <v>25</v>
@@ -7724,7 +7970,7 @@
         <v>35</v>
       </c>
       <c r="G138" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H138" t="s">
         <v>216</v>
@@ -7735,10 +7981,10 @@
         <v>17</v>
       </c>
       <c r="C139" t="s">
-        <v>615</v>
+        <v>697</v>
       </c>
       <c r="D139" t="s">
-        <v>616</v>
+        <v>698</v>
       </c>
       <c r="E139" t="s">
         <v>25</v>
@@ -7747,7 +7993,7 @@
         <v>35</v>
       </c>
       <c r="G139" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H139" t="s">
         <v>216</v>
@@ -7758,10 +8004,10 @@
         <v>17</v>
       </c>
       <c r="C140" t="s">
-        <v>617</v>
+        <v>699</v>
       </c>
       <c r="D140" t="s">
-        <v>618</v>
+        <v>700</v>
       </c>
       <c r="E140" t="s">
         <v>25</v>
@@ -7770,7 +8016,7 @@
         <v>35</v>
       </c>
       <c r="G140" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H140" t="s">
         <v>216</v>
@@ -7781,10 +8027,10 @@
         <v>17</v>
       </c>
       <c r="C141" t="s">
-        <v>619</v>
+        <v>701</v>
       </c>
       <c r="D141" t="s">
-        <v>620</v>
+        <v>702</v>
       </c>
       <c r="E141" t="s">
         <v>25</v>
@@ -7793,7 +8039,7 @@
         <v>35</v>
       </c>
       <c r="G141" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H141" t="s">
         <v>216</v>
@@ -7804,10 +8050,10 @@
         <v>17</v>
       </c>
       <c r="C142" t="s">
-        <v>621</v>
+        <v>703</v>
       </c>
       <c r="D142" t="s">
-        <v>622</v>
+        <v>704</v>
       </c>
       <c r="E142" t="s">
         <v>25</v>
@@ -7816,7 +8062,7 @@
         <v>35</v>
       </c>
       <c r="G142" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H142" t="s">
         <v>216</v>
@@ -7827,10 +8073,10 @@
         <v>17</v>
       </c>
       <c r="C143" t="s">
-        <v>623</v>
+        <v>705</v>
       </c>
       <c r="D143" t="s">
-        <v>624</v>
+        <v>706</v>
       </c>
       <c r="E143" t="s">
         <v>25</v>
@@ -7839,7 +8085,7 @@
         <v>35</v>
       </c>
       <c r="G143" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H143" t="s">
         <v>216</v>
@@ -7850,10 +8096,10 @@
         <v>17</v>
       </c>
       <c r="C144" t="s">
-        <v>625</v>
+        <v>707</v>
       </c>
       <c r="D144" t="s">
-        <v>626</v>
+        <v>708</v>
       </c>
       <c r="E144" t="s">
         <v>25</v>
@@ -7862,7 +8108,7 @@
         <v>35</v>
       </c>
       <c r="G144" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H144" t="s">
         <v>216</v>
@@ -7873,10 +8119,10 @@
         <v>17</v>
       </c>
       <c r="C145" t="s">
-        <v>627</v>
+        <v>709</v>
       </c>
       <c r="D145" t="s">
-        <v>628</v>
+        <v>710</v>
       </c>
       <c r="E145" t="s">
         <v>25</v>
@@ -7885,7 +8131,7 @@
         <v>35</v>
       </c>
       <c r="G145" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H145" t="s">
         <v>216</v>
@@ -7896,10 +8142,10 @@
         <v>17</v>
       </c>
       <c r="C146" t="s">
-        <v>629</v>
+        <v>711</v>
       </c>
       <c r="D146" t="s">
-        <v>630</v>
+        <v>712</v>
       </c>
       <c r="E146" t="s">
         <v>25</v>
@@ -7908,7 +8154,7 @@
         <v>35</v>
       </c>
       <c r="G146" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H146" t="s">
         <v>216</v>
@@ -7919,10 +8165,10 @@
         <v>17</v>
       </c>
       <c r="C147" t="s">
-        <v>631</v>
+        <v>713</v>
       </c>
       <c r="D147" t="s">
-        <v>632</v>
+        <v>714</v>
       </c>
       <c r="E147" t="s">
         <v>25</v>
@@ -7931,7 +8177,7 @@
         <v>35</v>
       </c>
       <c r="G147" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H147" t="s">
         <v>216</v>
@@ -7942,10 +8188,10 @@
         <v>17</v>
       </c>
       <c r="C148" t="s">
-        <v>633</v>
+        <v>715</v>
       </c>
       <c r="D148" t="s">
-        <v>634</v>
+        <v>716</v>
       </c>
       <c r="E148" t="s">
         <v>25</v>
@@ -7954,7 +8200,7 @@
         <v>35</v>
       </c>
       <c r="G148" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H148" t="s">
         <v>216</v>
@@ -7965,10 +8211,10 @@
         <v>17</v>
       </c>
       <c r="C149" t="s">
-        <v>635</v>
+        <v>717</v>
       </c>
       <c r="D149" t="s">
-        <v>636</v>
+        <v>718</v>
       </c>
       <c r="E149" t="s">
         <v>25</v>
@@ -7977,7 +8223,7 @@
         <v>35</v>
       </c>
       <c r="G149" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H149" t="s">
         <v>216</v>
@@ -7988,10 +8234,10 @@
         <v>17</v>
       </c>
       <c r="C150" t="s">
-        <v>637</v>
+        <v>719</v>
       </c>
       <c r="D150" t="s">
-        <v>638</v>
+        <v>720</v>
       </c>
       <c r="E150" t="s">
         <v>25</v>
@@ -8000,7 +8246,7 @@
         <v>35</v>
       </c>
       <c r="G150" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H150" t="s">
         <v>216</v>
@@ -8011,10 +8257,10 @@
         <v>17</v>
       </c>
       <c r="C151" t="s">
-        <v>639</v>
+        <v>721</v>
       </c>
       <c r="D151" t="s">
-        <v>640</v>
+        <v>722</v>
       </c>
       <c r="E151" t="s">
         <v>25</v>
@@ -8023,7 +8269,7 @@
         <v>35</v>
       </c>
       <c r="G151" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H151" t="s">
         <v>216</v>
@@ -8034,10 +8280,10 @@
         <v>17</v>
       </c>
       <c r="C152" t="s">
-        <v>641</v>
+        <v>723</v>
       </c>
       <c r="D152" t="s">
-        <v>642</v>
+        <v>724</v>
       </c>
       <c r="E152" t="s">
         <v>25</v>
@@ -8046,7 +8292,7 @@
         <v>35</v>
       </c>
       <c r="G152" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H152" t="s">
         <v>216</v>
@@ -8057,10 +8303,10 @@
         <v>17</v>
       </c>
       <c r="C153" t="s">
-        <v>643</v>
+        <v>725</v>
       </c>
       <c r="D153" t="s">
-        <v>644</v>
+        <v>726</v>
       </c>
       <c r="E153" t="s">
         <v>25</v>
@@ -8069,7 +8315,7 @@
         <v>35</v>
       </c>
       <c r="G153" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H153" t="s">
         <v>216</v>
@@ -8080,10 +8326,10 @@
         <v>17</v>
       </c>
       <c r="C154" t="s">
-        <v>645</v>
+        <v>727</v>
       </c>
       <c r="D154" t="s">
-        <v>646</v>
+        <v>728</v>
       </c>
       <c r="E154" t="s">
         <v>25</v>
@@ -8092,7 +8338,7 @@
         <v>35</v>
       </c>
       <c r="G154" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H154" t="s">
         <v>216</v>
@@ -8103,10 +8349,10 @@
         <v>17</v>
       </c>
       <c r="C155" t="s">
-        <v>647</v>
+        <v>729</v>
       </c>
       <c r="D155" t="s">
-        <v>648</v>
+        <v>730</v>
       </c>
       <c r="E155" t="s">
         <v>25</v>
@@ -8115,7 +8361,7 @@
         <v>35</v>
       </c>
       <c r="G155" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H155" t="s">
         <v>216</v>
@@ -8126,10 +8372,10 @@
         <v>17</v>
       </c>
       <c r="C156" t="s">
-        <v>649</v>
+        <v>731</v>
       </c>
       <c r="D156" t="s">
-        <v>650</v>
+        <v>732</v>
       </c>
       <c r="E156" t="s">
         <v>25</v>
@@ -8138,7 +8384,7 @@
         <v>35</v>
       </c>
       <c r="G156" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H156" t="s">
         <v>216</v>
@@ -8149,10 +8395,10 @@
         <v>17</v>
       </c>
       <c r="C157" t="s">
-        <v>651</v>
+        <v>733</v>
       </c>
       <c r="D157" t="s">
-        <v>652</v>
+        <v>734</v>
       </c>
       <c r="E157" t="s">
         <v>25</v>
@@ -8161,7 +8407,7 @@
         <v>35</v>
       </c>
       <c r="G157" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H157" t="s">
         <v>216</v>
@@ -8172,10 +8418,10 @@
         <v>17</v>
       </c>
       <c r="C158" t="s">
-        <v>653</v>
+        <v>735</v>
       </c>
       <c r="D158" t="s">
-        <v>654</v>
+        <v>736</v>
       </c>
       <c r="E158" t="s">
         <v>25</v>
@@ -8184,7 +8430,7 @@
         <v>35</v>
       </c>
       <c r="G158" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H158" t="s">
         <v>216</v>
@@ -8195,10 +8441,10 @@
         <v>17</v>
       </c>
       <c r="C159" t="s">
-        <v>655</v>
+        <v>737</v>
       </c>
       <c r="D159" t="s">
-        <v>656</v>
+        <v>738</v>
       </c>
       <c r="E159" t="s">
         <v>25</v>
@@ -8207,7 +8453,7 @@
         <v>35</v>
       </c>
       <c r="G159" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H159" t="s">
         <v>216</v>
@@ -8218,10 +8464,10 @@
         <v>17</v>
       </c>
       <c r="C160" t="s">
-        <v>657</v>
+        <v>739</v>
       </c>
       <c r="D160" t="s">
-        <v>658</v>
+        <v>740</v>
       </c>
       <c r="E160" t="s">
         <v>25</v>
@@ -8230,7 +8476,7 @@
         <v>35</v>
       </c>
       <c r="G160" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H160" t="s">
         <v>216</v>
@@ -8241,10 +8487,10 @@
         <v>17</v>
       </c>
       <c r="C161" t="s">
-        <v>659</v>
+        <v>741</v>
       </c>
       <c r="D161" t="s">
-        <v>660</v>
+        <v>742</v>
       </c>
       <c r="E161" t="s">
         <v>25</v>
@@ -8253,7 +8499,7 @@
         <v>35</v>
       </c>
       <c r="G161" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H161" t="s">
         <v>216</v>
@@ -8264,10 +8510,10 @@
         <v>17</v>
       </c>
       <c r="C162" t="s">
-        <v>661</v>
+        <v>743</v>
       </c>
       <c r="D162" t="s">
-        <v>662</v>
+        <v>744</v>
       </c>
       <c r="E162" t="s">
         <v>25</v>
@@ -8276,7 +8522,7 @@
         <v>35</v>
       </c>
       <c r="G162" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H162" t="s">
         <v>216</v>
@@ -8287,10 +8533,10 @@
         <v>17</v>
       </c>
       <c r="C163" t="s">
-        <v>663</v>
+        <v>745</v>
       </c>
       <c r="D163" t="s">
-        <v>664</v>
+        <v>746</v>
       </c>
       <c r="E163" t="s">
         <v>25</v>
@@ -8299,7 +8545,7 @@
         <v>35</v>
       </c>
       <c r="G163" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H163" t="s">
         <v>216</v>
@@ -8310,10 +8556,10 @@
         <v>17</v>
       </c>
       <c r="C164" t="s">
-        <v>665</v>
+        <v>747</v>
       </c>
       <c r="D164" t="s">
-        <v>666</v>
+        <v>748</v>
       </c>
       <c r="E164" t="s">
         <v>25</v>
@@ -8322,7 +8568,7 @@
         <v>35</v>
       </c>
       <c r="G164" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H164" t="s">
         <v>216</v>
@@ -8333,10 +8579,10 @@
         <v>17</v>
       </c>
       <c r="C165" t="s">
-        <v>667</v>
+        <v>749</v>
       </c>
       <c r="D165" t="s">
-        <v>668</v>
+        <v>750</v>
       </c>
       <c r="E165" t="s">
         <v>25</v>
@@ -8345,7 +8591,7 @@
         <v>35</v>
       </c>
       <c r="G165" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H165" t="s">
         <v>216</v>
@@ -8356,10 +8602,10 @@
         <v>17</v>
       </c>
       <c r="C166" t="s">
-        <v>669</v>
+        <v>751</v>
       </c>
       <c r="D166" t="s">
-        <v>670</v>
+        <v>752</v>
       </c>
       <c r="E166" t="s">
         <v>25</v>
@@ -8368,7 +8614,7 @@
         <v>35</v>
       </c>
       <c r="G166" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H166" t="s">
         <v>216</v>
@@ -8379,10 +8625,10 @@
         <v>17</v>
       </c>
       <c r="C167" t="s">
-        <v>671</v>
+        <v>753</v>
       </c>
       <c r="D167" t="s">
-        <v>672</v>
+        <v>754</v>
       </c>
       <c r="E167" t="s">
         <v>25</v>
@@ -8391,7 +8637,7 @@
         <v>35</v>
       </c>
       <c r="G167" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H167" t="s">
         <v>216</v>
@@ -8402,10 +8648,10 @@
         <v>17</v>
       </c>
       <c r="C168" t="s">
-        <v>673</v>
+        <v>755</v>
       </c>
       <c r="D168" t="s">
-        <v>674</v>
+        <v>756</v>
       </c>
       <c r="E168" t="s">
         <v>25</v>
@@ -8414,7 +8660,7 @@
         <v>35</v>
       </c>
       <c r="G168" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H168" t="s">
         <v>216</v>
@@ -8425,10 +8671,10 @@
         <v>17</v>
       </c>
       <c r="C169" t="s">
-        <v>675</v>
+        <v>757</v>
       </c>
       <c r="D169" t="s">
-        <v>676</v>
+        <v>758</v>
       </c>
       <c r="E169" t="s">
         <v>25</v>
@@ -8437,7 +8683,7 @@
         <v>35</v>
       </c>
       <c r="G169" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H169" t="s">
         <v>216</v>
@@ -8448,10 +8694,10 @@
         <v>17</v>
       </c>
       <c r="C170" t="s">
-        <v>677</v>
+        <v>759</v>
       </c>
       <c r="D170" t="s">
-        <v>678</v>
+        <v>760</v>
       </c>
       <c r="E170" t="s">
         <v>25</v>
@@ -8460,7 +8706,7 @@
         <v>35</v>
       </c>
       <c r="G170" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H170" t="s">
         <v>216</v>
@@ -8471,10 +8717,10 @@
         <v>17</v>
       </c>
       <c r="C171" t="s">
-        <v>679</v>
+        <v>761</v>
       </c>
       <c r="D171" t="s">
-        <v>680</v>
+        <v>762</v>
       </c>
       <c r="E171" t="s">
         <v>25</v>
@@ -8483,7 +8729,7 @@
         <v>35</v>
       </c>
       <c r="G171" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H171" t="s">
         <v>216</v>
@@ -8494,10 +8740,10 @@
         <v>17</v>
       </c>
       <c r="C172" t="s">
-        <v>681</v>
+        <v>763</v>
       </c>
       <c r="D172" t="s">
-        <v>682</v>
+        <v>764</v>
       </c>
       <c r="E172" t="s">
         <v>25</v>
@@ -8506,7 +8752,7 @@
         <v>35</v>
       </c>
       <c r="G172" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H172" t="s">
         <v>216</v>
@@ -8517,10 +8763,10 @@
         <v>17</v>
       </c>
       <c r="C173" t="s">
-        <v>683</v>
+        <v>765</v>
       </c>
       <c r="D173" t="s">
-        <v>684</v>
+        <v>766</v>
       </c>
       <c r="E173" t="s">
         <v>25</v>
@@ -8529,7 +8775,7 @@
         <v>35</v>
       </c>
       <c r="G173" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H173" t="s">
         <v>216</v>
@@ -8540,10 +8786,10 @@
         <v>17</v>
       </c>
       <c r="C174" t="s">
-        <v>685</v>
+        <v>767</v>
       </c>
       <c r="D174" t="s">
-        <v>686</v>
+        <v>768</v>
       </c>
       <c r="E174" t="s">
         <v>25</v>
@@ -8552,7 +8798,7 @@
         <v>35</v>
       </c>
       <c r="G174" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H174" t="s">
         <v>216</v>
@@ -8563,10 +8809,10 @@
         <v>17</v>
       </c>
       <c r="C175" t="s">
-        <v>687</v>
+        <v>769</v>
       </c>
       <c r="D175" t="s">
-        <v>688</v>
+        <v>770</v>
       </c>
       <c r="E175" t="s">
         <v>25</v>
@@ -8575,7 +8821,7 @@
         <v>35</v>
       </c>
       <c r="G175" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H175" t="s">
         <v>216</v>
@@ -8586,10 +8832,10 @@
         <v>17</v>
       </c>
       <c r="C176" t="s">
-        <v>689</v>
+        <v>771</v>
       </c>
       <c r="D176" t="s">
-        <v>690</v>
+        <v>772</v>
       </c>
       <c r="E176" t="s">
         <v>25</v>
@@ -8598,7 +8844,7 @@
         <v>35</v>
       </c>
       <c r="G176" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H176" t="s">
         <v>216</v>
@@ -8609,10 +8855,10 @@
         <v>17</v>
       </c>
       <c r="C177" t="s">
-        <v>691</v>
+        <v>773</v>
       </c>
       <c r="D177" t="s">
-        <v>692</v>
+        <v>774</v>
       </c>
       <c r="E177" t="s">
         <v>25</v>
@@ -8621,7 +8867,7 @@
         <v>35</v>
       </c>
       <c r="G177" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H177" t="s">
         <v>216</v>
@@ -8632,10 +8878,10 @@
         <v>17</v>
       </c>
       <c r="C178" t="s">
-        <v>693</v>
+        <v>775</v>
       </c>
       <c r="D178" t="s">
-        <v>694</v>
+        <v>776</v>
       </c>
       <c r="E178" t="s">
         <v>25</v>
@@ -8644,7 +8890,7 @@
         <v>35</v>
       </c>
       <c r="G178" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H178" t="s">
         <v>216</v>
@@ -8655,10 +8901,10 @@
         <v>17</v>
       </c>
       <c r="C179" t="s">
-        <v>695</v>
+        <v>777</v>
       </c>
       <c r="D179" t="s">
-        <v>696</v>
+        <v>778</v>
       </c>
       <c r="E179" t="s">
         <v>25</v>
@@ -8667,7 +8913,7 @@
         <v>35</v>
       </c>
       <c r="G179" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H179" t="s">
         <v>216</v>
@@ -8678,10 +8924,10 @@
         <v>17</v>
       </c>
       <c r="C180" t="s">
-        <v>697</v>
+        <v>779</v>
       </c>
       <c r="D180" t="s">
-        <v>698</v>
+        <v>780</v>
       </c>
       <c r="E180" t="s">
         <v>25</v>
@@ -8690,7 +8936,7 @@
         <v>35</v>
       </c>
       <c r="G180" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H180" t="s">
         <v>216</v>
@@ -8701,10 +8947,10 @@
         <v>17</v>
       </c>
       <c r="C181" t="s">
-        <v>699</v>
+        <v>781</v>
       </c>
       <c r="D181" t="s">
-        <v>700</v>
+        <v>782</v>
       </c>
       <c r="E181" t="s">
         <v>25</v>
@@ -8713,7 +8959,7 @@
         <v>35</v>
       </c>
       <c r="G181" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H181" t="s">
         <v>216</v>
@@ -8724,10 +8970,10 @@
         <v>17</v>
       </c>
       <c r="C182" t="s">
-        <v>701</v>
+        <v>783</v>
       </c>
       <c r="D182" t="s">
-        <v>702</v>
+        <v>784</v>
       </c>
       <c r="E182" t="s">
         <v>25</v>
@@ -8736,7 +8982,7 @@
         <v>35</v>
       </c>
       <c r="G182" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H182" t="s">
         <v>216</v>
@@ -8747,10 +8993,10 @@
         <v>17</v>
       </c>
       <c r="C183" t="s">
-        <v>703</v>
+        <v>785</v>
       </c>
       <c r="D183" t="s">
-        <v>704</v>
+        <v>786</v>
       </c>
       <c r="E183" t="s">
         <v>25</v>
@@ -8759,7 +9005,7 @@
         <v>35</v>
       </c>
       <c r="G183" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H183" t="s">
         <v>216</v>
@@ -8770,10 +9016,10 @@
         <v>17</v>
       </c>
       <c r="C184" t="s">
-        <v>705</v>
+        <v>787</v>
       </c>
       <c r="D184" t="s">
-        <v>706</v>
+        <v>788</v>
       </c>
       <c r="E184" t="s">
         <v>25</v>
@@ -8782,7 +9028,7 @@
         <v>35</v>
       </c>
       <c r="G184" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H184" t="s">
         <v>216</v>
@@ -8793,10 +9039,10 @@
         <v>17</v>
       </c>
       <c r="C185" t="s">
-        <v>707</v>
+        <v>789</v>
       </c>
       <c r="D185" t="s">
-        <v>708</v>
+        <v>790</v>
       </c>
       <c r="E185" t="s">
         <v>25</v>
@@ -8805,7 +9051,7 @@
         <v>35</v>
       </c>
       <c r="G185" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H185" t="s">
         <v>216</v>
@@ -8816,10 +9062,10 @@
         <v>17</v>
       </c>
       <c r="C186" t="s">
-        <v>709</v>
+        <v>791</v>
       </c>
       <c r="D186" t="s">
-        <v>710</v>
+        <v>792</v>
       </c>
       <c r="E186" t="s">
         <v>25</v>
@@ -8828,7 +9074,7 @@
         <v>35</v>
       </c>
       <c r="G186" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H186" t="s">
         <v>216</v>
@@ -8839,10 +9085,10 @@
         <v>17</v>
       </c>
       <c r="C187" t="s">
-        <v>711</v>
+        <v>793</v>
       </c>
       <c r="D187" t="s">
-        <v>712</v>
+        <v>794</v>
       </c>
       <c r="E187" t="s">
         <v>25</v>
@@ -8851,7 +9097,7 @@
         <v>35</v>
       </c>
       <c r="G187" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H187" t="s">
         <v>216</v>
@@ -8862,10 +9108,10 @@
         <v>17</v>
       </c>
       <c r="C188" t="s">
-        <v>713</v>
+        <v>795</v>
       </c>
       <c r="D188" t="s">
-        <v>714</v>
+        <v>796</v>
       </c>
       <c r="E188" t="s">
         <v>25</v>
@@ -8874,7 +9120,7 @@
         <v>35</v>
       </c>
       <c r="G188" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H188" t="s">
         <v>216</v>
@@ -8885,10 +9131,10 @@
         <v>17</v>
       </c>
       <c r="C189" t="s">
-        <v>715</v>
+        <v>797</v>
       </c>
       <c r="D189" t="s">
-        <v>716</v>
+        <v>798</v>
       </c>
       <c r="E189" t="s">
         <v>25</v>
@@ -8897,7 +9143,7 @@
         <v>35</v>
       </c>
       <c r="G189" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H189" t="s">
         <v>216</v>
@@ -8908,10 +9154,10 @@
         <v>17</v>
       </c>
       <c r="C190" t="s">
-        <v>717</v>
+        <v>799</v>
       </c>
       <c r="D190" t="s">
-        <v>718</v>
+        <v>800</v>
       </c>
       <c r="E190" t="s">
         <v>25</v>
@@ -8920,7 +9166,7 @@
         <v>35</v>
       </c>
       <c r="G190" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H190" t="s">
         <v>216</v>
@@ -8931,10 +9177,10 @@
         <v>17</v>
       </c>
       <c r="C191" t="s">
-        <v>719</v>
+        <v>801</v>
       </c>
       <c r="D191" t="s">
-        <v>720</v>
+        <v>802</v>
       </c>
       <c r="E191" t="s">
         <v>25</v>
@@ -8943,7 +9189,7 @@
         <v>35</v>
       </c>
       <c r="G191" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="H191" t="s">
         <v>216</v>
@@ -8956,7 +9202,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2F298A9-BCD9-4ABF-BE3B-9D1BDD3E7001}">
-  <dimension ref="B3:R69"/>
+  <dimension ref="B3:R110"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="11.19921875" bestFit="1" customWidth="1"/>
@@ -10551,6 +10797,826 @@
         <v>35</v>
       </c>
       <c r="R69" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="70" spans="13:18">
+      <c r="M70" t="s">
+        <v>17</v>
+      </c>
+      <c r="N70" t="s">
+        <v>345</v>
+      </c>
+      <c r="O70" t="s">
+        <v>346</v>
+      </c>
+      <c r="P70" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>35</v>
+      </c>
+      <c r="R70" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="71" spans="13:18">
+      <c r="M71" t="s">
+        <v>17</v>
+      </c>
+      <c r="N71" t="s">
+        <v>347</v>
+      </c>
+      <c r="O71" t="s">
+        <v>348</v>
+      </c>
+      <c r="P71" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>35</v>
+      </c>
+      <c r="R71" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="72" spans="13:18">
+      <c r="M72" t="s">
+        <v>17</v>
+      </c>
+      <c r="N72" t="s">
+        <v>349</v>
+      </c>
+      <c r="O72" t="s">
+        <v>350</v>
+      </c>
+      <c r="P72" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>35</v>
+      </c>
+      <c r="R72" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="73" spans="13:18">
+      <c r="M73" t="s">
+        <v>17</v>
+      </c>
+      <c r="N73" t="s">
+        <v>351</v>
+      </c>
+      <c r="O73" t="s">
+        <v>352</v>
+      </c>
+      <c r="P73" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>35</v>
+      </c>
+      <c r="R73" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="74" spans="13:18">
+      <c r="M74" t="s">
+        <v>17</v>
+      </c>
+      <c r="N74" t="s">
+        <v>353</v>
+      </c>
+      <c r="O74" t="s">
+        <v>354</v>
+      </c>
+      <c r="P74" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>35</v>
+      </c>
+      <c r="R74" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="75" spans="13:18">
+      <c r="M75" t="s">
+        <v>17</v>
+      </c>
+      <c r="N75" t="s">
+        <v>355</v>
+      </c>
+      <c r="O75" t="s">
+        <v>356</v>
+      </c>
+      <c r="P75" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>35</v>
+      </c>
+      <c r="R75" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="76" spans="13:18">
+      <c r="M76" t="s">
+        <v>17</v>
+      </c>
+      <c r="N76" t="s">
+        <v>357</v>
+      </c>
+      <c r="O76" t="s">
+        <v>358</v>
+      </c>
+      <c r="P76" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>35</v>
+      </c>
+      <c r="R76" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="77" spans="13:18">
+      <c r="M77" t="s">
+        <v>17</v>
+      </c>
+      <c r="N77" t="s">
+        <v>359</v>
+      </c>
+      <c r="O77" t="s">
+        <v>360</v>
+      </c>
+      <c r="P77" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>35</v>
+      </c>
+      <c r="R77" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="78" spans="13:18">
+      <c r="M78" t="s">
+        <v>17</v>
+      </c>
+      <c r="N78" t="s">
+        <v>361</v>
+      </c>
+      <c r="O78" t="s">
+        <v>362</v>
+      </c>
+      <c r="P78" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>35</v>
+      </c>
+      <c r="R78" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="79" spans="13:18">
+      <c r="M79" t="s">
+        <v>17</v>
+      </c>
+      <c r="N79" t="s">
+        <v>363</v>
+      </c>
+      <c r="O79" t="s">
+        <v>364</v>
+      </c>
+      <c r="P79" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>35</v>
+      </c>
+      <c r="R79" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="80" spans="13:18">
+      <c r="M80" t="s">
+        <v>17</v>
+      </c>
+      <c r="N80" t="s">
+        <v>365</v>
+      </c>
+      <c r="O80" t="s">
+        <v>366</v>
+      </c>
+      <c r="P80" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>35</v>
+      </c>
+      <c r="R80" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="81" spans="13:18">
+      <c r="M81" t="s">
+        <v>17</v>
+      </c>
+      <c r="N81" t="s">
+        <v>367</v>
+      </c>
+      <c r="O81" t="s">
+        <v>368</v>
+      </c>
+      <c r="P81" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>35</v>
+      </c>
+      <c r="R81" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="82" spans="13:18">
+      <c r="M82" t="s">
+        <v>17</v>
+      </c>
+      <c r="N82" t="s">
+        <v>369</v>
+      </c>
+      <c r="O82" t="s">
+        <v>370</v>
+      </c>
+      <c r="P82" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>35</v>
+      </c>
+      <c r="R82" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="83" spans="13:18">
+      <c r="M83" t="s">
+        <v>17</v>
+      </c>
+      <c r="N83" t="s">
+        <v>371</v>
+      </c>
+      <c r="O83" t="s">
+        <v>372</v>
+      </c>
+      <c r="P83" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>35</v>
+      </c>
+      <c r="R83" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="84" spans="13:18">
+      <c r="M84" t="s">
+        <v>17</v>
+      </c>
+      <c r="N84" t="s">
+        <v>373</v>
+      </c>
+      <c r="O84" t="s">
+        <v>374</v>
+      </c>
+      <c r="P84" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>35</v>
+      </c>
+      <c r="R84" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="85" spans="13:18">
+      <c r="M85" t="s">
+        <v>17</v>
+      </c>
+      <c r="N85" t="s">
+        <v>375</v>
+      </c>
+      <c r="O85" t="s">
+        <v>376</v>
+      </c>
+      <c r="P85" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>35</v>
+      </c>
+      <c r="R85" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="86" spans="13:18">
+      <c r="M86" t="s">
+        <v>17</v>
+      </c>
+      <c r="N86" t="s">
+        <v>377</v>
+      </c>
+      <c r="O86" t="s">
+        <v>378</v>
+      </c>
+      <c r="P86" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>35</v>
+      </c>
+      <c r="R86" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="87" spans="13:18">
+      <c r="M87" t="s">
+        <v>17</v>
+      </c>
+      <c r="N87" t="s">
+        <v>379</v>
+      </c>
+      <c r="O87" t="s">
+        <v>380</v>
+      </c>
+      <c r="P87" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>35</v>
+      </c>
+      <c r="R87" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="88" spans="13:18">
+      <c r="M88" t="s">
+        <v>17</v>
+      </c>
+      <c r="N88" t="s">
+        <v>381</v>
+      </c>
+      <c r="O88" t="s">
+        <v>382</v>
+      </c>
+      <c r="P88" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>35</v>
+      </c>
+      <c r="R88" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="89" spans="13:18">
+      <c r="M89" t="s">
+        <v>17</v>
+      </c>
+      <c r="N89" t="s">
+        <v>383</v>
+      </c>
+      <c r="O89" t="s">
+        <v>384</v>
+      </c>
+      <c r="P89" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>35</v>
+      </c>
+      <c r="R89" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="90" spans="13:18">
+      <c r="M90" t="s">
+        <v>17</v>
+      </c>
+      <c r="N90" t="s">
+        <v>385</v>
+      </c>
+      <c r="O90" t="s">
+        <v>386</v>
+      </c>
+      <c r="P90" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>35</v>
+      </c>
+      <c r="R90" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="91" spans="13:18">
+      <c r="M91" t="s">
+        <v>17</v>
+      </c>
+      <c r="N91" t="s">
+        <v>387</v>
+      </c>
+      <c r="O91" t="s">
+        <v>388</v>
+      </c>
+      <c r="P91" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>35</v>
+      </c>
+      <c r="R91" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="92" spans="13:18">
+      <c r="M92" t="s">
+        <v>17</v>
+      </c>
+      <c r="N92" t="s">
+        <v>389</v>
+      </c>
+      <c r="O92" t="s">
+        <v>390</v>
+      </c>
+      <c r="P92" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q92" t="s">
+        <v>35</v>
+      </c>
+      <c r="R92" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="93" spans="13:18">
+      <c r="M93" t="s">
+        <v>17</v>
+      </c>
+      <c r="N93" t="s">
+        <v>391</v>
+      </c>
+      <c r="O93" t="s">
+        <v>392</v>
+      </c>
+      <c r="P93" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q93" t="s">
+        <v>35</v>
+      </c>
+      <c r="R93" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="94" spans="13:18">
+      <c r="M94" t="s">
+        <v>17</v>
+      </c>
+      <c r="N94" t="s">
+        <v>393</v>
+      </c>
+      <c r="O94" t="s">
+        <v>394</v>
+      </c>
+      <c r="P94" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>35</v>
+      </c>
+      <c r="R94" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="95" spans="13:18">
+      <c r="M95" t="s">
+        <v>17</v>
+      </c>
+      <c r="N95" t="s">
+        <v>395</v>
+      </c>
+      <c r="O95" t="s">
+        <v>396</v>
+      </c>
+      <c r="P95" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>35</v>
+      </c>
+      <c r="R95" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="96" spans="13:18">
+      <c r="M96" t="s">
+        <v>17</v>
+      </c>
+      <c r="N96" t="s">
+        <v>397</v>
+      </c>
+      <c r="O96" t="s">
+        <v>398</v>
+      </c>
+      <c r="P96" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q96" t="s">
+        <v>35</v>
+      </c>
+      <c r="R96" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="97" spans="13:18">
+      <c r="M97" t="s">
+        <v>17</v>
+      </c>
+      <c r="N97" t="s">
+        <v>399</v>
+      </c>
+      <c r="O97" t="s">
+        <v>400</v>
+      </c>
+      <c r="P97" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>35</v>
+      </c>
+      <c r="R97" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="98" spans="13:18">
+      <c r="M98" t="s">
+        <v>17</v>
+      </c>
+      <c r="N98" t="s">
+        <v>401</v>
+      </c>
+      <c r="O98" t="s">
+        <v>402</v>
+      </c>
+      <c r="P98" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>35</v>
+      </c>
+      <c r="R98" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="99" spans="13:18">
+      <c r="M99" t="s">
+        <v>17</v>
+      </c>
+      <c r="N99" t="s">
+        <v>403</v>
+      </c>
+      <c r="O99" t="s">
+        <v>404</v>
+      </c>
+      <c r="P99" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q99" t="s">
+        <v>35</v>
+      </c>
+      <c r="R99" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="100" spans="13:18">
+      <c r="M100" t="s">
+        <v>17</v>
+      </c>
+      <c r="N100" t="s">
+        <v>405</v>
+      </c>
+      <c r="O100" t="s">
+        <v>406</v>
+      </c>
+      <c r="P100" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q100" t="s">
+        <v>35</v>
+      </c>
+      <c r="R100" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="101" spans="13:18">
+      <c r="M101" t="s">
+        <v>17</v>
+      </c>
+      <c r="N101" t="s">
+        <v>407</v>
+      </c>
+      <c r="O101" t="s">
+        <v>408</v>
+      </c>
+      <c r="P101" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>35</v>
+      </c>
+      <c r="R101" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="102" spans="13:18">
+      <c r="M102" t="s">
+        <v>17</v>
+      </c>
+      <c r="N102" t="s">
+        <v>409</v>
+      </c>
+      <c r="O102" t="s">
+        <v>410</v>
+      </c>
+      <c r="P102" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q102" t="s">
+        <v>35</v>
+      </c>
+      <c r="R102" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="103" spans="13:18">
+      <c r="M103" t="s">
+        <v>17</v>
+      </c>
+      <c r="N103" t="s">
+        <v>411</v>
+      </c>
+      <c r="O103" t="s">
+        <v>412</v>
+      </c>
+      <c r="P103" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q103" t="s">
+        <v>35</v>
+      </c>
+      <c r="R103" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="104" spans="13:18">
+      <c r="M104" t="s">
+        <v>17</v>
+      </c>
+      <c r="N104" t="s">
+        <v>413</v>
+      </c>
+      <c r="O104" t="s">
+        <v>414</v>
+      </c>
+      <c r="P104" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q104" t="s">
+        <v>35</v>
+      </c>
+      <c r="R104" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="105" spans="13:18">
+      <c r="M105" t="s">
+        <v>17</v>
+      </c>
+      <c r="N105" t="s">
+        <v>415</v>
+      </c>
+      <c r="O105" t="s">
+        <v>416</v>
+      </c>
+      <c r="P105" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q105" t="s">
+        <v>35</v>
+      </c>
+      <c r="R105" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="106" spans="13:18">
+      <c r="M106" t="s">
+        <v>17</v>
+      </c>
+      <c r="N106" t="s">
+        <v>417</v>
+      </c>
+      <c r="O106" t="s">
+        <v>418</v>
+      </c>
+      <c r="P106" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q106" t="s">
+        <v>35</v>
+      </c>
+      <c r="R106" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="107" spans="13:18">
+      <c r="M107" t="s">
+        <v>17</v>
+      </c>
+      <c r="N107" t="s">
+        <v>419</v>
+      </c>
+      <c r="O107" t="s">
+        <v>420</v>
+      </c>
+      <c r="P107" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q107" t="s">
+        <v>35</v>
+      </c>
+      <c r="R107" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="108" spans="13:18">
+      <c r="M108" t="s">
+        <v>17</v>
+      </c>
+      <c r="N108" t="s">
+        <v>421</v>
+      </c>
+      <c r="O108" t="s">
+        <v>422</v>
+      </c>
+      <c r="P108" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q108" t="s">
+        <v>35</v>
+      </c>
+      <c r="R108" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="109" spans="13:18">
+      <c r="M109" t="s">
+        <v>17</v>
+      </c>
+      <c r="N109" t="s">
+        <v>423</v>
+      </c>
+      <c r="O109" t="s">
+        <v>424</v>
+      </c>
+      <c r="P109" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q109" t="s">
+        <v>35</v>
+      </c>
+      <c r="R109" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="110" spans="13:18">
+      <c r="M110" t="s">
+        <v>17</v>
+      </c>
+      <c r="N110" t="s">
+        <v>425</v>
+      </c>
+      <c r="O110" t="s">
+        <v>426</v>
+      </c>
+      <c r="P110" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q110" t="s">
+        <v>35</v>
+      </c>
+      <c r="R110" t="s">
         <v>216</v>
       </c>
     </row>

--- a/VerveStacks_JPN_grids/SysSettings.xlsx
+++ b/VerveStacks_JPN_grids/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BD9EB72-249C-4294-90A6-F1426694E180}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{077C15E3-0EDE-4022-90D9-6EAFEE755479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3308" yWindow="3308" windowWidth="21600" windowHeight="12682" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -4862,7 +4862,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D56F767-9A8C-483E-8E5B-C8746E992E0C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44D0AF1E-68EF-4066-9A76-937E2BFC0735}">
   <dimension ref="B3:H191"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SysSettings.xlsx
+++ b/VerveStacks_JPN_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{077C15E3-0EDE-4022-90D9-6EAFEE755479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96FC9584-78A5-438F-9EC0-EE3CCC9E8E86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4862,7 +4862,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44D0AF1E-68EF-4066-9A76-937E2BFC0735}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01F46E78-DE05-4F2E-8A17-8FD4A9FCD10F}">
   <dimension ref="B3:H191"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SysSettings.xlsx
+++ b/VerveStacks_JPN_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96FC9584-78A5-438F-9EC0-EE3CCC9E8E86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99C0B827-5E83-4862-A5C6-EBD5DC3E0F9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4862,7 +4862,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01F46E78-DE05-4F2E-8A17-8FD4A9FCD10F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30ECF209-EEE8-4AD3-B99F-4C53B9F5AEBF}">
   <dimension ref="B3:H191"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SysSettings.xlsx
+++ b/VerveStacks_JPN_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99C0B827-5E83-4862-A5C6-EBD5DC3E0F9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FE0DDE7-3150-4E2A-9476-BB2D730D01E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4862,7 +4862,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30ECF209-EEE8-4AD3-B99F-4C53B9F5AEBF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE9801EF-4BE4-4D0B-A6D2-695626E6329C}">
   <dimension ref="B3:H191"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SysSettings.xlsx
+++ b/VerveStacks_JPN_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FE0DDE7-3150-4E2A-9476-BB2D730D01E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29208DDE-1300-4DDA-B662-7BC7C0A92E97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4862,7 +4862,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE9801EF-4BE4-4D0B-A6D2-695626E6329C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC21F59E-2118-4B46-B3BF-D63DA1C49489}">
   <dimension ref="B3:H191"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SysSettings.xlsx
+++ b/VerveStacks_JPN_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8E8FC44-5DFC-4EF5-9CB6-900474455539}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B450AD1E-60AC-407D-ADCC-1214F28B4181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4862,7 +4862,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{182646AE-8AAF-4091-BAEE-6F872CEFFD10}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B930B46D-DEC6-4546-B42A-2271E84CD7B3}">
   <dimension ref="B3:H191"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SysSettings.xlsx
+++ b/VerveStacks_JPN_grids/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B450AD1E-60AC-407D-ADCC-1214F28B4181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B094630-9ABC-41B9-B6D8-239C854E8B19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -4862,7 +4862,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B930B46D-DEC6-4546-B42A-2271E84CD7B3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5FE800C-E4A6-4A71-83C1-BDEFDAAE86F7}">
   <dimension ref="B3:H191"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SysSettings.xlsx
+++ b/VerveStacks_JPN_grids/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B094630-9ABC-41B9-B6D8-239C854E8B19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{934FD37C-1927-4B0C-B310-C4071E662284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -4862,7 +4862,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5FE800C-E4A6-4A71-83C1-BDEFDAAE86F7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBB3F415-5B8E-47D4-BCA0-ED1AAB5F9455}">
   <dimension ref="B3:H191"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SysSettings.xlsx
+++ b/VerveStacks_JPN_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{934FD37C-1927-4B0C-B310-C4071E662284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86321B7D-53E2-4C0B-9197-51178B9F985B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4862,7 +4862,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBB3F415-5B8E-47D4-BCA0-ED1AAB5F9455}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1CD0B84-17CF-441B-9D36-8909B3403126}">
   <dimension ref="B3:H191"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SysSettings.xlsx
+++ b/VerveStacks_JPN_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86321B7D-53E2-4C0B-9197-51178B9F985B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD4E2EC5-2230-4D44-9D3D-5D955A3159A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4862,7 +4862,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1CD0B84-17CF-441B-9D36-8909B3403126}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{505C449D-9304-461A-91C2-0EEBFFF5FE5E}">
   <dimension ref="B3:H191"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SysSettings.xlsx
+++ b/VerveStacks_JPN_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD4E2EC5-2230-4D44-9D3D-5D955A3159A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F70D219A-435D-417A-BEBB-ECD5310FA15E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4862,7 +4862,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{505C449D-9304-461A-91C2-0EEBFFF5FE5E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B8186DB-C8F0-431D-ABAD-AD0D3EA5F72F}">
   <dimension ref="B3:H191"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SysSettings.xlsx
+++ b/VerveStacks_JPN_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F70D219A-435D-417A-BEBB-ECD5310FA15E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FADE896A-C7F0-4D34-B6A0-BDE99C9CD4CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4862,7 +4862,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B8186DB-C8F0-431D-ABAD-AD0D3EA5F72F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE9F7AB1-B95E-47F4-8A38-A311625EAEF9}">
   <dimension ref="B3:H191"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SysSettings.xlsx
+++ b/VerveStacks_JPN_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FADE896A-C7F0-4D34-B6A0-BDE99C9CD4CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{637E495E-039D-4555-9651-A5ABE8FFCFD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4862,7 +4862,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE9F7AB1-B95E-47F4-8A38-A311625EAEF9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0EB2DF9-C184-40E7-9FFB-328DFD3004DC}">
   <dimension ref="B3:H191"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SysSettings.xlsx
+++ b/VerveStacks_JPN_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{637E495E-039D-4555-9651-A5ABE8FFCFD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B91A0498-CBE8-4E5F-A613-5FB4ECE6E4F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4862,7 +4862,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0EB2DF9-C184-40E7-9FFB-328DFD3004DC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68CFDCE4-B4CC-486E-BB52-746BC132D3AC}">
   <dimension ref="B3:H191"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SysSettings.xlsx
+++ b/VerveStacks_JPN_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B91A0498-CBE8-4E5F-A613-5FB4ECE6E4F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C43661B-3A0E-4322-8312-B58BC498DC83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4862,7 +4862,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68CFDCE4-B4CC-486E-BB52-746BC132D3AC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{513A710C-3BF3-4731-AE51-BD24BE84BD25}">
   <dimension ref="B3:H191"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SysSettings.xlsx
+++ b/VerveStacks_JPN_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C43661B-3A0E-4322-8312-B58BC498DC83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{792ACA97-126F-4541-9092-23F8B40829A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4862,7 +4862,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{513A710C-3BF3-4731-AE51-BD24BE84BD25}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C471D5E0-1B3C-4CC8-84A8-7FFDD5596C31}">
   <dimension ref="B3:H191"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SysSettings.xlsx
+++ b/VerveStacks_JPN_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{792ACA97-126F-4541-9092-23F8B40829A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{006E0389-4CE4-4D0A-9D94-30AE6A07FB30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4862,7 +4862,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C471D5E0-1B3C-4CC8-84A8-7FFDD5596C31}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3B8650C-BE89-434A-9C06-C84BB7609E32}">
   <dimension ref="B3:H191"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SysSettings.xlsx
+++ b/VerveStacks_JPN_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{006E0389-4CE4-4D0A-9D94-30AE6A07FB30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49BFE090-3367-41A9-9F82-4FE2AE719802}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4862,7 +4862,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3B8650C-BE89-434A-9C06-C84BB7609E32}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F003653E-D288-45FD-A3B0-642D06AAC8FE}">
   <dimension ref="B3:H191"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SysSettings.xlsx
+++ b/VerveStacks_JPN_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49BFE090-3367-41A9-9F82-4FE2AE719802}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0F00786-1467-48B3-9077-1F17127F8E0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4862,7 +4862,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F003653E-D288-45FD-A3B0-642D06AAC8FE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24E5868F-9928-4D85-97CC-E54593EE97F8}">
   <dimension ref="B3:H191"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SysSettings.xlsx
+++ b/VerveStacks_JPN_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0F00786-1467-48B3-9077-1F17127F8E0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCF76A8F-6DEB-4E3E-B19F-C1D67AD9B579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4862,7 +4862,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24E5868F-9928-4D85-97CC-E54593EE97F8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{134F1AB1-5D86-4FEA-B961-7E1D8E9FCBDC}">
   <dimension ref="B3:H191"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SysSettings.xlsx
+++ b/VerveStacks_JPN_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5D00EB6-8486-4543-B56D-B7D518E23890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E283719B-3EF7-48CC-9144-A9F7EB17C423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7571,7 +7571,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CB3E84C-22BA-4541-B0D4-113D36AF05BF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{596072DB-43C3-4A98-9C51-32B0650C9613}">
   <dimension ref="B3:H191"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SysSettings.xlsx
+++ b/VerveStacks_JPN_grids/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E283719B-3EF7-48CC-9144-A9F7EB17C423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4C3C296-8EED-4D1C-9C63-222877A814FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2506" uniqueCount="804">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2500" uniqueCount="802">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -867,12 +867,6 @@
   </si>
   <si>
     <t>solar electricity generation in cluster -- 30</t>
-  </si>
-  <si>
-    <t>elc_spv_031</t>
-  </si>
-  <si>
-    <t>solar electricity generation in cluster -- 31</t>
   </si>
   <si>
     <t>elc_wof_001</t>
@@ -4866,7 +4860,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2F298A9-BCD9-4ABF-BE3B-9D1BDD3E7001}">
-  <dimension ref="B3:R110"/>
+  <dimension ref="B3:R109"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="11.19921875" bestFit="1" customWidth="1"/>
@@ -7261,26 +7255,6 @@
         <v>35</v>
       </c>
       <c r="R109" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="110" spans="13:18">
-      <c r="M110" t="s">
-        <v>17</v>
-      </c>
-      <c r="N110" t="s">
-        <v>426</v>
-      </c>
-      <c r="O110" t="s">
-        <v>427</v>
-      </c>
-      <c r="P110" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q110" t="s">
-        <v>35</v>
-      </c>
-      <c r="R110" t="s">
         <v>217</v>
       </c>
     </row>
@@ -7571,13 +7545,13 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{596072DB-43C3-4A98-9C51-32B0650C9613}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EA3C1FE-2F77-4658-8D9D-9FDCA1B420DF}">
   <dimension ref="B3:H191"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="3" spans="2:8">
       <c r="B3" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="4" spans="2:8">
@@ -7608,10 +7582,10 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D5" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="E5" t="s">
         <v>25</v>
@@ -7620,7 +7594,7 @@
         <v>35</v>
       </c>
       <c r="G5" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H5" t="s">
         <v>217</v>
@@ -7631,10 +7605,10 @@
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="E6" t="s">
         <v>25</v>
@@ -7643,7 +7617,7 @@
         <v>35</v>
       </c>
       <c r="G6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H6" t="s">
         <v>217</v>
@@ -7654,10 +7628,10 @@
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D7" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="E7" t="s">
         <v>25</v>
@@ -7666,7 +7640,7 @@
         <v>35</v>
       </c>
       <c r="G7" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H7" t="s">
         <v>217</v>
@@ -7677,10 +7651,10 @@
         <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D8" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E8" t="s">
         <v>25</v>
@@ -7689,7 +7663,7 @@
         <v>35</v>
       </c>
       <c r="G8" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H8" t="s">
         <v>217</v>
@@ -7700,10 +7674,10 @@
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D9" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E9" t="s">
         <v>25</v>
@@ -7712,7 +7686,7 @@
         <v>35</v>
       </c>
       <c r="G9" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H9" t="s">
         <v>217</v>
@@ -7723,10 +7697,10 @@
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="D10" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="E10" t="s">
         <v>25</v>
@@ -7735,7 +7709,7 @@
         <v>35</v>
       </c>
       <c r="G10" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H10" t="s">
         <v>217</v>
@@ -7746,10 +7720,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D11" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E11" t="s">
         <v>25</v>
@@ -7758,7 +7732,7 @@
         <v>35</v>
       </c>
       <c r="G11" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H11" t="s">
         <v>217</v>
@@ -7769,10 +7743,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D12" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="E12" t="s">
         <v>25</v>
@@ -7781,7 +7755,7 @@
         <v>35</v>
       </c>
       <c r="G12" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H12" t="s">
         <v>217</v>
@@ -7792,10 +7766,10 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D13" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E13" t="s">
         <v>25</v>
@@ -7804,7 +7778,7 @@
         <v>35</v>
       </c>
       <c r="G13" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H13" t="s">
         <v>217</v>
@@ -7815,10 +7789,10 @@
         <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D14" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="E14" t="s">
         <v>25</v>
@@ -7827,7 +7801,7 @@
         <v>35</v>
       </c>
       <c r="G14" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H14" t="s">
         <v>217</v>
@@ -7838,10 +7812,10 @@
         <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D15" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="E15" t="s">
         <v>25</v>
@@ -7850,7 +7824,7 @@
         <v>35</v>
       </c>
       <c r="G15" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H15" t="s">
         <v>217</v>
@@ -7861,10 +7835,10 @@
         <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="D16" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="E16" t="s">
         <v>25</v>
@@ -7873,7 +7847,7 @@
         <v>35</v>
       </c>
       <c r="G16" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H16" t="s">
         <v>217</v>
@@ -7884,10 +7858,10 @@
         <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="D17" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="E17" t="s">
         <v>25</v>
@@ -7896,7 +7870,7 @@
         <v>35</v>
       </c>
       <c r="G17" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H17" t="s">
         <v>217</v>
@@ -7907,10 +7881,10 @@
         <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="D18" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="E18" t="s">
         <v>25</v>
@@ -7919,7 +7893,7 @@
         <v>35</v>
       </c>
       <c r="G18" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H18" t="s">
         <v>217</v>
@@ -7930,10 +7904,10 @@
         <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="D19" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E19" t="s">
         <v>25</v>
@@ -7942,7 +7916,7 @@
         <v>35</v>
       </c>
       <c r="G19" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H19" t="s">
         <v>217</v>
@@ -7953,10 +7927,10 @@
         <v>17</v>
       </c>
       <c r="C20" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D20" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="E20" t="s">
         <v>25</v>
@@ -7965,7 +7939,7 @@
         <v>35</v>
       </c>
       <c r="G20" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H20" t="s">
         <v>217</v>
@@ -7976,10 +7950,10 @@
         <v>17</v>
       </c>
       <c r="C21" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D21" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="E21" t="s">
         <v>25</v>
@@ -7988,7 +7962,7 @@
         <v>35</v>
       </c>
       <c r="G21" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H21" t="s">
         <v>217</v>
@@ -7999,10 +7973,10 @@
         <v>17</v>
       </c>
       <c r="C22" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="D22" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="E22" t="s">
         <v>25</v>
@@ -8011,7 +7985,7 @@
         <v>35</v>
       </c>
       <c r="G22" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H22" t="s">
         <v>217</v>
@@ -8022,10 +7996,10 @@
         <v>17</v>
       </c>
       <c r="C23" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="D23" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E23" t="s">
         <v>25</v>
@@ -8034,7 +8008,7 @@
         <v>35</v>
       </c>
       <c r="G23" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H23" t="s">
         <v>217</v>
@@ -8045,10 +8019,10 @@
         <v>17</v>
       </c>
       <c r="C24" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="D24" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="E24" t="s">
         <v>25</v>
@@ -8057,7 +8031,7 @@
         <v>35</v>
       </c>
       <c r="G24" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H24" t="s">
         <v>217</v>
@@ -8068,10 +8042,10 @@
         <v>17</v>
       </c>
       <c r="C25" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D25" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="E25" t="s">
         <v>25</v>
@@ -8080,7 +8054,7 @@
         <v>35</v>
       </c>
       <c r="G25" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H25" t="s">
         <v>217</v>
@@ -8091,10 +8065,10 @@
         <v>17</v>
       </c>
       <c r="C26" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="D26" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="E26" t="s">
         <v>25</v>
@@ -8103,7 +8077,7 @@
         <v>35</v>
       </c>
       <c r="G26" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H26" t="s">
         <v>217</v>
@@ -8114,10 +8088,10 @@
         <v>17</v>
       </c>
       <c r="C27" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D27" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="E27" t="s">
         <v>25</v>
@@ -8126,7 +8100,7 @@
         <v>35</v>
       </c>
       <c r="G27" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H27" t="s">
         <v>217</v>
@@ -8137,10 +8111,10 @@
         <v>17</v>
       </c>
       <c r="C28" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D28" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="E28" t="s">
         <v>25</v>
@@ -8149,7 +8123,7 @@
         <v>35</v>
       </c>
       <c r="G28" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H28" t="s">
         <v>217</v>
@@ -8160,10 +8134,10 @@
         <v>17</v>
       </c>
       <c r="C29" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="D29" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="E29" t="s">
         <v>25</v>
@@ -8172,7 +8146,7 @@
         <v>35</v>
       </c>
       <c r="G29" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H29" t="s">
         <v>217</v>
@@ -8183,10 +8157,10 @@
         <v>17</v>
       </c>
       <c r="C30" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="D30" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E30" t="s">
         <v>25</v>
@@ -8195,7 +8169,7 @@
         <v>35</v>
       </c>
       <c r="G30" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H30" t="s">
         <v>217</v>
@@ -8206,10 +8180,10 @@
         <v>17</v>
       </c>
       <c r="C31" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="D31" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="E31" t="s">
         <v>25</v>
@@ -8218,7 +8192,7 @@
         <v>35</v>
       </c>
       <c r="G31" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H31" t="s">
         <v>217</v>
@@ -8229,10 +8203,10 @@
         <v>17</v>
       </c>
       <c r="C32" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="D32" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="E32" t="s">
         <v>25</v>
@@ -8241,7 +8215,7 @@
         <v>35</v>
       </c>
       <c r="G32" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H32" t="s">
         <v>217</v>
@@ -8252,10 +8226,10 @@
         <v>17</v>
       </c>
       <c r="C33" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D33" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="E33" t="s">
         <v>25</v>
@@ -8264,7 +8238,7 @@
         <v>35</v>
       </c>
       <c r="G33" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H33" t="s">
         <v>217</v>
@@ -8275,10 +8249,10 @@
         <v>17</v>
       </c>
       <c r="C34" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D34" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="E34" t="s">
         <v>25</v>
@@ -8287,7 +8261,7 @@
         <v>35</v>
       </c>
       <c r="G34" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H34" t="s">
         <v>217</v>
@@ -8298,10 +8272,10 @@
         <v>17</v>
       </c>
       <c r="C35" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="D35" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="E35" t="s">
         <v>25</v>
@@ -8310,7 +8284,7 @@
         <v>35</v>
       </c>
       <c r="G35" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H35" t="s">
         <v>217</v>
@@ -8321,10 +8295,10 @@
         <v>17</v>
       </c>
       <c r="C36" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D36" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="E36" t="s">
         <v>25</v>
@@ -8333,7 +8307,7 @@
         <v>35</v>
       </c>
       <c r="G36" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H36" t="s">
         <v>217</v>
@@ -8344,10 +8318,10 @@
         <v>17</v>
       </c>
       <c r="C37" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="D37" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="E37" t="s">
         <v>25</v>
@@ -8356,7 +8330,7 @@
         <v>35</v>
       </c>
       <c r="G37" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H37" t="s">
         <v>217</v>
@@ -8367,10 +8341,10 @@
         <v>17</v>
       </c>
       <c r="C38" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D38" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="E38" t="s">
         <v>25</v>
@@ -8379,7 +8353,7 @@
         <v>35</v>
       </c>
       <c r="G38" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H38" t="s">
         <v>217</v>
@@ -8390,10 +8364,10 @@
         <v>17</v>
       </c>
       <c r="C39" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D39" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="E39" t="s">
         <v>25</v>
@@ -8402,7 +8376,7 @@
         <v>35</v>
       </c>
       <c r="G39" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H39" t="s">
         <v>217</v>
@@ -8413,10 +8387,10 @@
         <v>17</v>
       </c>
       <c r="C40" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="D40" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="E40" t="s">
         <v>25</v>
@@ -8425,7 +8399,7 @@
         <v>35</v>
       </c>
       <c r="G40" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H40" t="s">
         <v>217</v>
@@ -8436,10 +8410,10 @@
         <v>17</v>
       </c>
       <c r="C41" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D41" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="E41" t="s">
         <v>25</v>
@@ -8448,7 +8422,7 @@
         <v>35</v>
       </c>
       <c r="G41" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H41" t="s">
         <v>217</v>
@@ -8459,10 +8433,10 @@
         <v>17</v>
       </c>
       <c r="C42" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="D42" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="E42" t="s">
         <v>25</v>
@@ -8471,7 +8445,7 @@
         <v>35</v>
       </c>
       <c r="G42" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H42" t="s">
         <v>217</v>
@@ -8482,10 +8456,10 @@
         <v>17</v>
       </c>
       <c r="C43" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="D43" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="E43" t="s">
         <v>25</v>
@@ -8494,7 +8468,7 @@
         <v>35</v>
       </c>
       <c r="G43" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H43" t="s">
         <v>217</v>
@@ -8505,10 +8479,10 @@
         <v>17</v>
       </c>
       <c r="C44" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D44" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="E44" t="s">
         <v>25</v>
@@ -8517,7 +8491,7 @@
         <v>35</v>
       </c>
       <c r="G44" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H44" t="s">
         <v>217</v>
@@ -8528,10 +8502,10 @@
         <v>17</v>
       </c>
       <c r="C45" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D45" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E45" t="s">
         <v>25</v>
@@ -8540,7 +8514,7 @@
         <v>35</v>
       </c>
       <c r="G45" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H45" t="s">
         <v>217</v>
@@ -8551,10 +8525,10 @@
         <v>17</v>
       </c>
       <c r="C46" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="D46" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="E46" t="s">
         <v>25</v>
@@ -8563,7 +8537,7 @@
         <v>35</v>
       </c>
       <c r="G46" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H46" t="s">
         <v>217</v>
@@ -8574,10 +8548,10 @@
         <v>17</v>
       </c>
       <c r="C47" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="D47" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="E47" t="s">
         <v>25</v>
@@ -8586,7 +8560,7 @@
         <v>35</v>
       </c>
       <c r="G47" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H47" t="s">
         <v>217</v>
@@ -8597,10 +8571,10 @@
         <v>17</v>
       </c>
       <c r="C48" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="D48" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="E48" t="s">
         <v>25</v>
@@ -8609,7 +8583,7 @@
         <v>35</v>
       </c>
       <c r="G48" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H48" t="s">
         <v>217</v>
@@ -8620,10 +8594,10 @@
         <v>17</v>
       </c>
       <c r="C49" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D49" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="E49" t="s">
         <v>25</v>
@@ -8632,7 +8606,7 @@
         <v>35</v>
       </c>
       <c r="G49" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H49" t="s">
         <v>217</v>
@@ -8643,10 +8617,10 @@
         <v>17</v>
       </c>
       <c r="C50" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="D50" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="E50" t="s">
         <v>25</v>
@@ -8655,7 +8629,7 @@
         <v>35</v>
       </c>
       <c r="G50" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H50" t="s">
         <v>217</v>
@@ -8666,10 +8640,10 @@
         <v>17</v>
       </c>
       <c r="C51" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="D51" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="E51" t="s">
         <v>25</v>
@@ -8678,7 +8652,7 @@
         <v>35</v>
       </c>
       <c r="G51" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H51" t="s">
         <v>217</v>
@@ -8689,10 +8663,10 @@
         <v>17</v>
       </c>
       <c r="C52" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="D52" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="E52" t="s">
         <v>25</v>
@@ -8701,7 +8675,7 @@
         <v>35</v>
       </c>
       <c r="G52" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H52" t="s">
         <v>217</v>
@@ -8712,10 +8686,10 @@
         <v>17</v>
       </c>
       <c r="C53" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="D53" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="E53" t="s">
         <v>25</v>
@@ -8724,7 +8698,7 @@
         <v>35</v>
       </c>
       <c r="G53" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H53" t="s">
         <v>217</v>
@@ -8735,10 +8709,10 @@
         <v>17</v>
       </c>
       <c r="C54" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="D54" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="E54" t="s">
         <v>25</v>
@@ -8747,7 +8721,7 @@
         <v>35</v>
       </c>
       <c r="G54" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H54" t="s">
         <v>217</v>
@@ -8758,10 +8732,10 @@
         <v>17</v>
       </c>
       <c r="C55" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="D55" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="E55" t="s">
         <v>25</v>
@@ -8770,7 +8744,7 @@
         <v>35</v>
       </c>
       <c r="G55" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H55" t="s">
         <v>217</v>
@@ -8781,10 +8755,10 @@
         <v>17</v>
       </c>
       <c r="C56" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="D56" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="E56" t="s">
         <v>25</v>
@@ -8793,7 +8767,7 @@
         <v>35</v>
       </c>
       <c r="G56" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H56" t="s">
         <v>217</v>
@@ -8804,10 +8778,10 @@
         <v>17</v>
       </c>
       <c r="C57" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="D57" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="E57" t="s">
         <v>25</v>
@@ -8816,7 +8790,7 @@
         <v>35</v>
       </c>
       <c r="G57" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H57" t="s">
         <v>217</v>
@@ -8827,10 +8801,10 @@
         <v>17</v>
       </c>
       <c r="C58" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="D58" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="E58" t="s">
         <v>25</v>
@@ -8839,7 +8813,7 @@
         <v>35</v>
       </c>
       <c r="G58" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H58" t="s">
         <v>217</v>
@@ -8850,10 +8824,10 @@
         <v>17</v>
       </c>
       <c r="C59" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D59" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="E59" t="s">
         <v>25</v>
@@ -8862,7 +8836,7 @@
         <v>35</v>
       </c>
       <c r="G59" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H59" t="s">
         <v>217</v>
@@ -8873,10 +8847,10 @@
         <v>17</v>
       </c>
       <c r="C60" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="D60" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="E60" t="s">
         <v>25</v>
@@ -8885,7 +8859,7 @@
         <v>35</v>
       </c>
       <c r="G60" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H60" t="s">
         <v>217</v>
@@ -8896,10 +8870,10 @@
         <v>17</v>
       </c>
       <c r="C61" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="D61" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="E61" t="s">
         <v>25</v>
@@ -8908,7 +8882,7 @@
         <v>35</v>
       </c>
       <c r="G61" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H61" t="s">
         <v>217</v>
@@ -8919,10 +8893,10 @@
         <v>17</v>
       </c>
       <c r="C62" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="D62" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="E62" t="s">
         <v>25</v>
@@ -8931,7 +8905,7 @@
         <v>35</v>
       </c>
       <c r="G62" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H62" t="s">
         <v>217</v>
@@ -8942,10 +8916,10 @@
         <v>17</v>
       </c>
       <c r="C63" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="D63" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="E63" t="s">
         <v>25</v>
@@ -8954,7 +8928,7 @@
         <v>35</v>
       </c>
       <c r="G63" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H63" t="s">
         <v>217</v>
@@ -8965,10 +8939,10 @@
         <v>17</v>
       </c>
       <c r="C64" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="D64" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="E64" t="s">
         <v>25</v>
@@ -8977,7 +8951,7 @@
         <v>35</v>
       </c>
       <c r="G64" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H64" t="s">
         <v>217</v>
@@ -8988,10 +8962,10 @@
         <v>17</v>
       </c>
       <c r="C65" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="D65" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="E65" t="s">
         <v>25</v>
@@ -9000,7 +8974,7 @@
         <v>35</v>
       </c>
       <c r="G65" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H65" t="s">
         <v>217</v>
@@ -9011,10 +8985,10 @@
         <v>17</v>
       </c>
       <c r="C66" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="D66" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="E66" t="s">
         <v>25</v>
@@ -9023,7 +8997,7 @@
         <v>35</v>
       </c>
       <c r="G66" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H66" t="s">
         <v>217</v>
@@ -9034,10 +9008,10 @@
         <v>17</v>
       </c>
       <c r="C67" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="D67" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="E67" t="s">
         <v>25</v>
@@ -9046,7 +9020,7 @@
         <v>35</v>
       </c>
       <c r="G67" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H67" t="s">
         <v>217</v>
@@ -9057,10 +9031,10 @@
         <v>17</v>
       </c>
       <c r="C68" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="D68" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="E68" t="s">
         <v>25</v>
@@ -9069,7 +9043,7 @@
         <v>35</v>
       </c>
       <c r="G68" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H68" t="s">
         <v>217</v>
@@ -9080,10 +9054,10 @@
         <v>17</v>
       </c>
       <c r="C69" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="D69" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="E69" t="s">
         <v>25</v>
@@ -9092,7 +9066,7 @@
         <v>35</v>
       </c>
       <c r="G69" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H69" t="s">
         <v>217</v>
@@ -9103,10 +9077,10 @@
         <v>17</v>
       </c>
       <c r="C70" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="D70" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="E70" t="s">
         <v>25</v>
@@ -9115,7 +9089,7 @@
         <v>35</v>
       </c>
       <c r="G70" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H70" t="s">
         <v>217</v>
@@ -9126,10 +9100,10 @@
         <v>17</v>
       </c>
       <c r="C71" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="D71" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="E71" t="s">
         <v>25</v>
@@ -9138,7 +9112,7 @@
         <v>35</v>
       </c>
       <c r="G71" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H71" t="s">
         <v>217</v>
@@ -9149,10 +9123,10 @@
         <v>17</v>
       </c>
       <c r="C72" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="D72" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="E72" t="s">
         <v>25</v>
@@ -9161,7 +9135,7 @@
         <v>35</v>
       </c>
       <c r="G72" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H72" t="s">
         <v>217</v>
@@ -9172,10 +9146,10 @@
         <v>17</v>
       </c>
       <c r="C73" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D73" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="E73" t="s">
         <v>25</v>
@@ -9184,7 +9158,7 @@
         <v>35</v>
       </c>
       <c r="G73" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H73" t="s">
         <v>217</v>
@@ -9195,10 +9169,10 @@
         <v>17</v>
       </c>
       <c r="C74" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="D74" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="E74" t="s">
         <v>25</v>
@@ -9207,7 +9181,7 @@
         <v>35</v>
       </c>
       <c r="G74" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H74" t="s">
         <v>217</v>
@@ -9218,10 +9192,10 @@
         <v>17</v>
       </c>
       <c r="C75" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="D75" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="E75" t="s">
         <v>25</v>
@@ -9230,7 +9204,7 @@
         <v>35</v>
       </c>
       <c r="G75" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H75" t="s">
         <v>217</v>
@@ -9241,10 +9215,10 @@
         <v>17</v>
       </c>
       <c r="C76" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="D76" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="E76" t="s">
         <v>25</v>
@@ -9253,7 +9227,7 @@
         <v>35</v>
       </c>
       <c r="G76" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H76" t="s">
         <v>217</v>
@@ -9264,10 +9238,10 @@
         <v>17</v>
       </c>
       <c r="C77" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="D77" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="E77" t="s">
         <v>25</v>
@@ -9276,7 +9250,7 @@
         <v>35</v>
       </c>
       <c r="G77" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H77" t="s">
         <v>217</v>
@@ -9287,10 +9261,10 @@
         <v>17</v>
       </c>
       <c r="C78" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="D78" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="E78" t="s">
         <v>25</v>
@@ -9299,7 +9273,7 @@
         <v>35</v>
       </c>
       <c r="G78" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H78" t="s">
         <v>217</v>
@@ -9310,10 +9284,10 @@
         <v>17</v>
       </c>
       <c r="C79" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="D79" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="E79" t="s">
         <v>25</v>
@@ -9322,7 +9296,7 @@
         <v>35</v>
       </c>
       <c r="G79" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H79" t="s">
         <v>217</v>
@@ -9333,10 +9307,10 @@
         <v>17</v>
       </c>
       <c r="C80" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="D80" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="E80" t="s">
         <v>25</v>
@@ -9345,7 +9319,7 @@
         <v>35</v>
       </c>
       <c r="G80" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H80" t="s">
         <v>217</v>
@@ -9356,10 +9330,10 @@
         <v>17</v>
       </c>
       <c r="C81" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="D81" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="E81" t="s">
         <v>25</v>
@@ -9368,7 +9342,7 @@
         <v>35</v>
       </c>
       <c r="G81" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H81" t="s">
         <v>217</v>
@@ -9379,10 +9353,10 @@
         <v>17</v>
       </c>
       <c r="C82" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="D82" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="E82" t="s">
         <v>25</v>
@@ -9391,7 +9365,7 @@
         <v>35</v>
       </c>
       <c r="G82" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H82" t="s">
         <v>217</v>
@@ -9402,10 +9376,10 @@
         <v>17</v>
       </c>
       <c r="C83" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="D83" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="E83" t="s">
         <v>25</v>
@@ -9414,7 +9388,7 @@
         <v>35</v>
       </c>
       <c r="G83" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H83" t="s">
         <v>217</v>
@@ -9425,10 +9399,10 @@
         <v>17</v>
       </c>
       <c r="C84" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="D84" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E84" t="s">
         <v>25</v>
@@ -9437,7 +9411,7 @@
         <v>35</v>
       </c>
       <c r="G84" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H84" t="s">
         <v>217</v>
@@ -9448,10 +9422,10 @@
         <v>17</v>
       </c>
       <c r="C85" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="D85" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="E85" t="s">
         <v>25</v>
@@ -9460,7 +9434,7 @@
         <v>35</v>
       </c>
       <c r="G85" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H85" t="s">
         <v>217</v>
@@ -9471,10 +9445,10 @@
         <v>17</v>
       </c>
       <c r="C86" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="D86" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="E86" t="s">
         <v>25</v>
@@ -9483,7 +9457,7 @@
         <v>35</v>
       </c>
       <c r="G86" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H86" t="s">
         <v>217</v>
@@ -9494,10 +9468,10 @@
         <v>17</v>
       </c>
       <c r="C87" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="D87" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="E87" t="s">
         <v>25</v>
@@ -9506,7 +9480,7 @@
         <v>35</v>
       </c>
       <c r="G87" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H87" t="s">
         <v>217</v>
@@ -9517,10 +9491,10 @@
         <v>17</v>
       </c>
       <c r="C88" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="D88" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="E88" t="s">
         <v>25</v>
@@ -9529,7 +9503,7 @@
         <v>35</v>
       </c>
       <c r="G88" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H88" t="s">
         <v>217</v>
@@ -9540,10 +9514,10 @@
         <v>17</v>
       </c>
       <c r="C89" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="D89" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="E89" t="s">
         <v>25</v>
@@ -9552,7 +9526,7 @@
         <v>35</v>
       </c>
       <c r="G89" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H89" t="s">
         <v>217</v>
@@ -9563,10 +9537,10 @@
         <v>17</v>
       </c>
       <c r="C90" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="D90" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E90" t="s">
         <v>25</v>
@@ -9575,7 +9549,7 @@
         <v>35</v>
       </c>
       <c r="G90" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H90" t="s">
         <v>217</v>
@@ -9586,10 +9560,10 @@
         <v>17</v>
       </c>
       <c r="C91" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="D91" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E91" t="s">
         <v>25</v>
@@ -9598,7 +9572,7 @@
         <v>35</v>
       </c>
       <c r="G91" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H91" t="s">
         <v>217</v>
@@ -9609,10 +9583,10 @@
         <v>17</v>
       </c>
       <c r="C92" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="D92" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="E92" t="s">
         <v>25</v>
@@ -9621,7 +9595,7 @@
         <v>35</v>
       </c>
       <c r="G92" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H92" t="s">
         <v>217</v>
@@ -9632,10 +9606,10 @@
         <v>17</v>
       </c>
       <c r="C93" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="D93" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E93" t="s">
         <v>25</v>
@@ -9644,7 +9618,7 @@
         <v>35</v>
       </c>
       <c r="G93" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H93" t="s">
         <v>217</v>
@@ -9655,10 +9629,10 @@
         <v>17</v>
       </c>
       <c r="C94" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="D94" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="E94" t="s">
         <v>25</v>
@@ -9667,7 +9641,7 @@
         <v>35</v>
       </c>
       <c r="G94" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H94" t="s">
         <v>217</v>
@@ -9678,10 +9652,10 @@
         <v>17</v>
       </c>
       <c r="C95" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="D95" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="E95" t="s">
         <v>25</v>
@@ -9690,7 +9664,7 @@
         <v>35</v>
       </c>
       <c r="G95" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H95" t="s">
         <v>217</v>
@@ -9701,10 +9675,10 @@
         <v>17</v>
       </c>
       <c r="C96" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="D96" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="E96" t="s">
         <v>25</v>
@@ -9713,7 +9687,7 @@
         <v>35</v>
       </c>
       <c r="G96" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H96" t="s">
         <v>217</v>
@@ -9724,10 +9698,10 @@
         <v>17</v>
       </c>
       <c r="C97" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="D97" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="E97" t="s">
         <v>25</v>
@@ -9736,7 +9710,7 @@
         <v>35</v>
       </c>
       <c r="G97" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H97" t="s">
         <v>217</v>
@@ -9747,10 +9721,10 @@
         <v>17</v>
       </c>
       <c r="C98" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="D98" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="E98" t="s">
         <v>25</v>
@@ -9759,7 +9733,7 @@
         <v>35</v>
       </c>
       <c r="G98" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H98" t="s">
         <v>217</v>
@@ -9770,10 +9744,10 @@
         <v>17</v>
       </c>
       <c r="C99" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="D99" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="E99" t="s">
         <v>25</v>
@@ -9782,7 +9756,7 @@
         <v>35</v>
       </c>
       <c r="G99" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H99" t="s">
         <v>217</v>
@@ -9793,10 +9767,10 @@
         <v>17</v>
       </c>
       <c r="C100" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="D100" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="E100" t="s">
         <v>25</v>
@@ -9805,7 +9779,7 @@
         <v>35</v>
       </c>
       <c r="G100" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H100" t="s">
         <v>217</v>
@@ -9816,10 +9790,10 @@
         <v>17</v>
       </c>
       <c r="C101" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="D101" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="E101" t="s">
         <v>25</v>
@@ -9828,7 +9802,7 @@
         <v>35</v>
       </c>
       <c r="G101" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H101" t="s">
         <v>217</v>
@@ -9839,10 +9813,10 @@
         <v>17</v>
       </c>
       <c r="C102" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="D102" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="E102" t="s">
         <v>25</v>
@@ -9851,7 +9825,7 @@
         <v>35</v>
       </c>
       <c r="G102" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H102" t="s">
         <v>217</v>
@@ -9862,10 +9836,10 @@
         <v>17</v>
       </c>
       <c r="C103" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="D103" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="E103" t="s">
         <v>25</v>
@@ -9874,7 +9848,7 @@
         <v>35</v>
       </c>
       <c r="G103" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H103" t="s">
         <v>217</v>
@@ -9885,10 +9859,10 @@
         <v>17</v>
       </c>
       <c r="C104" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="D104" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="E104" t="s">
         <v>25</v>
@@ -9897,7 +9871,7 @@
         <v>35</v>
       </c>
       <c r="G104" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H104" t="s">
         <v>217</v>
@@ -9908,10 +9882,10 @@
         <v>17</v>
       </c>
       <c r="C105" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="D105" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E105" t="s">
         <v>25</v>
@@ -9920,7 +9894,7 @@
         <v>35</v>
       </c>
       <c r="G105" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H105" t="s">
         <v>217</v>
@@ -9931,10 +9905,10 @@
         <v>17</v>
       </c>
       <c r="C106" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="D106" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="E106" t="s">
         <v>25</v>
@@ -9943,7 +9917,7 @@
         <v>35</v>
       </c>
       <c r="G106" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H106" t="s">
         <v>217</v>
@@ -9954,10 +9928,10 @@
         <v>17</v>
       </c>
       <c r="C107" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="D107" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="E107" t="s">
         <v>25</v>
@@ -9966,7 +9940,7 @@
         <v>35</v>
       </c>
       <c r="G107" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H107" t="s">
         <v>217</v>
@@ -9977,10 +9951,10 @@
         <v>17</v>
       </c>
       <c r="C108" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="D108" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="E108" t="s">
         <v>25</v>
@@ -9989,7 +9963,7 @@
         <v>35</v>
       </c>
       <c r="G108" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H108" t="s">
         <v>217</v>
@@ -10000,10 +9974,10 @@
         <v>17</v>
       </c>
       <c r="C109" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="D109" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="E109" t="s">
         <v>25</v>
@@ -10012,7 +9986,7 @@
         <v>35</v>
       </c>
       <c r="G109" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H109" t="s">
         <v>217</v>
@@ -10023,10 +9997,10 @@
         <v>17</v>
       </c>
       <c r="C110" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="D110" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="E110" t="s">
         <v>25</v>
@@ -10035,7 +10009,7 @@
         <v>35</v>
       </c>
       <c r="G110" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H110" t="s">
         <v>217</v>
@@ -10046,10 +10020,10 @@
         <v>17</v>
       </c>
       <c r="C111" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="D111" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="E111" t="s">
         <v>25</v>
@@ -10058,7 +10032,7 @@
         <v>35</v>
       </c>
       <c r="G111" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H111" t="s">
         <v>217</v>
@@ -10069,10 +10043,10 @@
         <v>17</v>
       </c>
       <c r="C112" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="D112" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="E112" t="s">
         <v>25</v>
@@ -10081,7 +10055,7 @@
         <v>35</v>
       </c>
       <c r="G112" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H112" t="s">
         <v>217</v>
@@ -10092,10 +10066,10 @@
         <v>17</v>
       </c>
       <c r="C113" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="D113" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="E113" t="s">
         <v>25</v>
@@ -10104,7 +10078,7 @@
         <v>35</v>
       </c>
       <c r="G113" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H113" t="s">
         <v>217</v>
@@ -10115,10 +10089,10 @@
         <v>17</v>
       </c>
       <c r="C114" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="D114" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="E114" t="s">
         <v>25</v>
@@ -10127,7 +10101,7 @@
         <v>35</v>
       </c>
       <c r="G114" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H114" t="s">
         <v>217</v>
@@ -10138,10 +10112,10 @@
         <v>17</v>
       </c>
       <c r="C115" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="D115" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="E115" t="s">
         <v>25</v>
@@ -10150,7 +10124,7 @@
         <v>35</v>
       </c>
       <c r="G115" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H115" t="s">
         <v>217</v>
@@ -10161,10 +10135,10 @@
         <v>17</v>
       </c>
       <c r="C116" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="D116" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E116" t="s">
         <v>25</v>
@@ -10173,7 +10147,7 @@
         <v>35</v>
       </c>
       <c r="G116" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H116" t="s">
         <v>217</v>
@@ -10184,10 +10158,10 @@
         <v>17</v>
       </c>
       <c r="C117" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D117" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="E117" t="s">
         <v>25</v>
@@ -10196,7 +10170,7 @@
         <v>35</v>
       </c>
       <c r="G117" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H117" t="s">
         <v>217</v>
@@ -10207,10 +10181,10 @@
         <v>17</v>
       </c>
       <c r="C118" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D118" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="E118" t="s">
         <v>25</v>
@@ -10219,7 +10193,7 @@
         <v>35</v>
       </c>
       <c r="G118" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H118" t="s">
         <v>217</v>
@@ -10230,10 +10204,10 @@
         <v>17</v>
       </c>
       <c r="C119" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="D119" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="E119" t="s">
         <v>25</v>
@@ -10242,7 +10216,7 @@
         <v>35</v>
       </c>
       <c r="G119" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H119" t="s">
         <v>217</v>
@@ -10253,10 +10227,10 @@
         <v>17</v>
       </c>
       <c r="C120" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="D120" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E120" t="s">
         <v>25</v>
@@ -10265,7 +10239,7 @@
         <v>35</v>
       </c>
       <c r="G120" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H120" t="s">
         <v>217</v>
@@ -10276,10 +10250,10 @@
         <v>17</v>
       </c>
       <c r="C121" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="D121" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="E121" t="s">
         <v>25</v>
@@ -10288,7 +10262,7 @@
         <v>35</v>
       </c>
       <c r="G121" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H121" t="s">
         <v>217</v>
@@ -10299,10 +10273,10 @@
         <v>17</v>
       </c>
       <c r="C122" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D122" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E122" t="s">
         <v>25</v>
@@ -10311,7 +10285,7 @@
         <v>35</v>
       </c>
       <c r="G122" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H122" t="s">
         <v>217</v>
@@ -10322,10 +10296,10 @@
         <v>17</v>
       </c>
       <c r="C123" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="D123" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="E123" t="s">
         <v>25</v>
@@ -10334,7 +10308,7 @@
         <v>35</v>
       </c>
       <c r="G123" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H123" t="s">
         <v>217</v>
@@ -10345,10 +10319,10 @@
         <v>17</v>
       </c>
       <c r="C124" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="D124" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="E124" t="s">
         <v>25</v>
@@ -10357,7 +10331,7 @@
         <v>35</v>
       </c>
       <c r="G124" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H124" t="s">
         <v>217</v>
@@ -10368,10 +10342,10 @@
         <v>17</v>
       </c>
       <c r="C125" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="D125" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="E125" t="s">
         <v>25</v>
@@ -10380,7 +10354,7 @@
         <v>35</v>
       </c>
       <c r="G125" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H125" t="s">
         <v>217</v>
@@ -10391,10 +10365,10 @@
         <v>17</v>
       </c>
       <c r="C126" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="D126" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="E126" t="s">
         <v>25</v>
@@ -10403,7 +10377,7 @@
         <v>35</v>
       </c>
       <c r="G126" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H126" t="s">
         <v>217</v>
@@ -10414,10 +10388,10 @@
         <v>17</v>
       </c>
       <c r="C127" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="D127" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="E127" t="s">
         <v>25</v>
@@ -10426,7 +10400,7 @@
         <v>35</v>
       </c>
       <c r="G127" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H127" t="s">
         <v>217</v>
@@ -10437,10 +10411,10 @@
         <v>17</v>
       </c>
       <c r="C128" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="D128" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="E128" t="s">
         <v>25</v>
@@ -10449,7 +10423,7 @@
         <v>35</v>
       </c>
       <c r="G128" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H128" t="s">
         <v>217</v>
@@ -10460,10 +10434,10 @@
         <v>17</v>
       </c>
       <c r="C129" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D129" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="E129" t="s">
         <v>25</v>
@@ -10472,7 +10446,7 @@
         <v>35</v>
       </c>
       <c r="G129" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H129" t="s">
         <v>217</v>
@@ -10483,10 +10457,10 @@
         <v>17</v>
       </c>
       <c r="C130" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="D130" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="E130" t="s">
         <v>25</v>
@@ -10495,7 +10469,7 @@
         <v>35</v>
       </c>
       <c r="G130" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H130" t="s">
         <v>217</v>
@@ -10506,10 +10480,10 @@
         <v>17</v>
       </c>
       <c r="C131" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="D131" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="E131" t="s">
         <v>25</v>
@@ -10518,7 +10492,7 @@
         <v>35</v>
       </c>
       <c r="G131" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H131" t="s">
         <v>217</v>
@@ -10529,10 +10503,10 @@
         <v>17</v>
       </c>
       <c r="C132" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="D132" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="E132" t="s">
         <v>25</v>
@@ -10541,7 +10515,7 @@
         <v>35</v>
       </c>
       <c r="G132" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H132" t="s">
         <v>217</v>
@@ -10552,10 +10526,10 @@
         <v>17</v>
       </c>
       <c r="C133" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="D133" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="E133" t="s">
         <v>25</v>
@@ -10564,7 +10538,7 @@
         <v>35</v>
       </c>
       <c r="G133" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H133" t="s">
         <v>217</v>
@@ -10575,10 +10549,10 @@
         <v>17</v>
       </c>
       <c r="C134" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="D134" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="E134" t="s">
         <v>25</v>
@@ -10587,7 +10561,7 @@
         <v>35</v>
       </c>
       <c r="G134" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H134" t="s">
         <v>217</v>
@@ -10598,10 +10572,10 @@
         <v>17</v>
       </c>
       <c r="C135" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="D135" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="E135" t="s">
         <v>25</v>
@@ -10610,7 +10584,7 @@
         <v>35</v>
       </c>
       <c r="G135" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H135" t="s">
         <v>217</v>
@@ -10621,10 +10595,10 @@
         <v>17</v>
       </c>
       <c r="C136" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="D136" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="E136" t="s">
         <v>25</v>
@@ -10633,7 +10607,7 @@
         <v>35</v>
       </c>
       <c r="G136" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H136" t="s">
         <v>217</v>
@@ -10644,10 +10618,10 @@
         <v>17</v>
       </c>
       <c r="C137" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="D137" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="E137" t="s">
         <v>25</v>
@@ -10656,7 +10630,7 @@
         <v>35</v>
       </c>
       <c r="G137" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H137" t="s">
         <v>217</v>
@@ -10667,10 +10641,10 @@
         <v>17</v>
       </c>
       <c r="C138" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="D138" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="E138" t="s">
         <v>25</v>
@@ -10679,7 +10653,7 @@
         <v>35</v>
       </c>
       <c r="G138" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H138" t="s">
         <v>217</v>
@@ -10690,10 +10664,10 @@
         <v>17</v>
       </c>
       <c r="C139" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="D139" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="E139" t="s">
         <v>25</v>
@@ -10702,7 +10676,7 @@
         <v>35</v>
       </c>
       <c r="G139" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H139" t="s">
         <v>217</v>
@@ -10713,10 +10687,10 @@
         <v>17</v>
       </c>
       <c r="C140" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="D140" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="E140" t="s">
         <v>25</v>
@@ -10725,7 +10699,7 @@
         <v>35</v>
       </c>
       <c r="G140" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H140" t="s">
         <v>217</v>
@@ -10736,10 +10710,10 @@
         <v>17</v>
       </c>
       <c r="C141" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="D141" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="E141" t="s">
         <v>25</v>
@@ -10748,7 +10722,7 @@
         <v>35</v>
       </c>
       <c r="G141" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H141" t="s">
         <v>217</v>
@@ -10759,10 +10733,10 @@
         <v>17</v>
       </c>
       <c r="C142" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="D142" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="E142" t="s">
         <v>25</v>
@@ -10771,7 +10745,7 @@
         <v>35</v>
       </c>
       <c r="G142" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H142" t="s">
         <v>217</v>
@@ -10782,10 +10756,10 @@
         <v>17</v>
       </c>
       <c r="C143" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="D143" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="E143" t="s">
         <v>25</v>
@@ -10794,7 +10768,7 @@
         <v>35</v>
       </c>
       <c r="G143" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H143" t="s">
         <v>217</v>
@@ -10805,10 +10779,10 @@
         <v>17</v>
       </c>
       <c r="C144" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="D144" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="E144" t="s">
         <v>25</v>
@@ -10817,7 +10791,7 @@
         <v>35</v>
       </c>
       <c r="G144" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H144" t="s">
         <v>217</v>
@@ -10828,10 +10802,10 @@
         <v>17</v>
       </c>
       <c r="C145" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="D145" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="E145" t="s">
         <v>25</v>
@@ -10840,7 +10814,7 @@
         <v>35</v>
       </c>
       <c r="G145" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H145" t="s">
         <v>217</v>
@@ -10851,10 +10825,10 @@
         <v>17</v>
       </c>
       <c r="C146" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="D146" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="E146" t="s">
         <v>25</v>
@@ -10863,7 +10837,7 @@
         <v>35</v>
       </c>
       <c r="G146" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H146" t="s">
         <v>217</v>
@@ -10874,10 +10848,10 @@
         <v>17</v>
       </c>
       <c r="C147" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="D147" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="E147" t="s">
         <v>25</v>
@@ -10886,7 +10860,7 @@
         <v>35</v>
       </c>
       <c r="G147" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H147" t="s">
         <v>217</v>
@@ -10897,10 +10871,10 @@
         <v>17</v>
       </c>
       <c r="C148" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="D148" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="E148" t="s">
         <v>25</v>
@@ -10909,7 +10883,7 @@
         <v>35</v>
       </c>
       <c r="G148" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H148" t="s">
         <v>217</v>
@@ -10920,10 +10894,10 @@
         <v>17</v>
       </c>
       <c r="C149" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="D149" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="E149" t="s">
         <v>25</v>
@@ -10932,7 +10906,7 @@
         <v>35</v>
       </c>
       <c r="G149" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H149" t="s">
         <v>217</v>
@@ -10943,10 +10917,10 @@
         <v>17</v>
       </c>
       <c r="C150" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="D150" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="E150" t="s">
         <v>25</v>
@@ -10955,7 +10929,7 @@
         <v>35</v>
       </c>
       <c r="G150" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H150" t="s">
         <v>217</v>
@@ -10966,10 +10940,10 @@
         <v>17</v>
       </c>
       <c r="C151" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="D151" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="E151" t="s">
         <v>25</v>
@@ -10978,7 +10952,7 @@
         <v>35</v>
       </c>
       <c r="G151" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H151" t="s">
         <v>217</v>
@@ -10989,10 +10963,10 @@
         <v>17</v>
       </c>
       <c r="C152" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="D152" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="E152" t="s">
         <v>25</v>
@@ -11001,7 +10975,7 @@
         <v>35</v>
       </c>
       <c r="G152" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H152" t="s">
         <v>217</v>
@@ -11012,10 +10986,10 @@
         <v>17</v>
       </c>
       <c r="C153" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="D153" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="E153" t="s">
         <v>25</v>
@@ -11024,7 +10998,7 @@
         <v>35</v>
       </c>
       <c r="G153" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H153" t="s">
         <v>217</v>
@@ -11035,10 +11009,10 @@
         <v>17</v>
       </c>
       <c r="C154" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="D154" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="E154" t="s">
         <v>25</v>
@@ -11047,7 +11021,7 @@
         <v>35</v>
       </c>
       <c r="G154" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H154" t="s">
         <v>217</v>
@@ -11058,10 +11032,10 @@
         <v>17</v>
       </c>
       <c r="C155" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="D155" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="E155" t="s">
         <v>25</v>
@@ -11070,7 +11044,7 @@
         <v>35</v>
       </c>
       <c r="G155" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H155" t="s">
         <v>217</v>
@@ -11081,10 +11055,10 @@
         <v>17</v>
       </c>
       <c r="C156" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="D156" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="E156" t="s">
         <v>25</v>
@@ -11093,7 +11067,7 @@
         <v>35</v>
       </c>
       <c r="G156" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H156" t="s">
         <v>217</v>
@@ -11104,10 +11078,10 @@
         <v>17</v>
       </c>
       <c r="C157" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="D157" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="E157" t="s">
         <v>25</v>
@@ -11116,7 +11090,7 @@
         <v>35</v>
       </c>
       <c r="G157" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H157" t="s">
         <v>217</v>
@@ -11127,10 +11101,10 @@
         <v>17</v>
       </c>
       <c r="C158" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="D158" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="E158" t="s">
         <v>25</v>
@@ -11139,7 +11113,7 @@
         <v>35</v>
       </c>
       <c r="G158" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H158" t="s">
         <v>217</v>
@@ -11150,10 +11124,10 @@
         <v>17</v>
       </c>
       <c r="C159" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="D159" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="E159" t="s">
         <v>25</v>
@@ -11162,7 +11136,7 @@
         <v>35</v>
       </c>
       <c r="G159" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H159" t="s">
         <v>217</v>
@@ -11173,10 +11147,10 @@
         <v>17</v>
       </c>
       <c r="C160" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="D160" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="E160" t="s">
         <v>25</v>
@@ -11185,7 +11159,7 @@
         <v>35</v>
       </c>
       <c r="G160" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H160" t="s">
         <v>217</v>
@@ -11196,10 +11170,10 @@
         <v>17</v>
       </c>
       <c r="C161" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="D161" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="E161" t="s">
         <v>25</v>
@@ -11208,7 +11182,7 @@
         <v>35</v>
       </c>
       <c r="G161" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H161" t="s">
         <v>217</v>
@@ -11219,10 +11193,10 @@
         <v>17</v>
       </c>
       <c r="C162" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="D162" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="E162" t="s">
         <v>25</v>
@@ -11231,7 +11205,7 @@
         <v>35</v>
       </c>
       <c r="G162" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H162" t="s">
         <v>217</v>
@@ -11242,10 +11216,10 @@
         <v>17</v>
       </c>
       <c r="C163" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="D163" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="E163" t="s">
         <v>25</v>
@@ -11254,7 +11228,7 @@
         <v>35</v>
       </c>
       <c r="G163" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H163" t="s">
         <v>217</v>
@@ -11265,10 +11239,10 @@
         <v>17</v>
       </c>
       <c r="C164" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="D164" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="E164" t="s">
         <v>25</v>
@@ -11277,7 +11251,7 @@
         <v>35</v>
       </c>
       <c r="G164" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H164" t="s">
         <v>217</v>
@@ -11288,10 +11262,10 @@
         <v>17</v>
       </c>
       <c r="C165" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="D165" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="E165" t="s">
         <v>25</v>
@@ -11300,7 +11274,7 @@
         <v>35</v>
       </c>
       <c r="G165" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H165" t="s">
         <v>217</v>
@@ -11311,10 +11285,10 @@
         <v>17</v>
       </c>
       <c r="C166" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="D166" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="E166" t="s">
         <v>25</v>
@@ -11323,7 +11297,7 @@
         <v>35</v>
       </c>
       <c r="G166" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H166" t="s">
         <v>217</v>
@@ -11334,10 +11308,10 @@
         <v>17</v>
       </c>
       <c r="C167" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="D167" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="E167" t="s">
         <v>25</v>
@@ -11346,7 +11320,7 @@
         <v>35</v>
       </c>
       <c r="G167" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H167" t="s">
         <v>217</v>
@@ -11357,10 +11331,10 @@
         <v>17</v>
       </c>
       <c r="C168" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="D168" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="E168" t="s">
         <v>25</v>
@@ -11369,7 +11343,7 @@
         <v>35</v>
       </c>
       <c r="G168" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H168" t="s">
         <v>217</v>
@@ -11380,10 +11354,10 @@
         <v>17</v>
       </c>
       <c r="C169" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="D169" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="E169" t="s">
         <v>25</v>
@@ -11392,7 +11366,7 @@
         <v>35</v>
       </c>
       <c r="G169" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H169" t="s">
         <v>217</v>
@@ -11403,10 +11377,10 @@
         <v>17</v>
       </c>
       <c r="C170" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="D170" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="E170" t="s">
         <v>25</v>
@@ -11415,7 +11389,7 @@
         <v>35</v>
       </c>
       <c r="G170" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H170" t="s">
         <v>217</v>
@@ -11426,10 +11400,10 @@
         <v>17</v>
       </c>
       <c r="C171" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="D171" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="E171" t="s">
         <v>25</v>
@@ -11438,7 +11412,7 @@
         <v>35</v>
       </c>
       <c r="G171" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H171" t="s">
         <v>217</v>
@@ -11449,10 +11423,10 @@
         <v>17</v>
       </c>
       <c r="C172" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="D172" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="E172" t="s">
         <v>25</v>
@@ -11461,7 +11435,7 @@
         <v>35</v>
       </c>
       <c r="G172" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H172" t="s">
         <v>217</v>
@@ -11472,10 +11446,10 @@
         <v>17</v>
       </c>
       <c r="C173" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="D173" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="E173" t="s">
         <v>25</v>
@@ -11484,7 +11458,7 @@
         <v>35</v>
       </c>
       <c r="G173" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H173" t="s">
         <v>217</v>
@@ -11495,10 +11469,10 @@
         <v>17</v>
       </c>
       <c r="C174" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D174" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="E174" t="s">
         <v>25</v>
@@ -11507,7 +11481,7 @@
         <v>35</v>
       </c>
       <c r="G174" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H174" t="s">
         <v>217</v>
@@ -11518,10 +11492,10 @@
         <v>17</v>
       </c>
       <c r="C175" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="D175" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="E175" t="s">
         <v>25</v>
@@ -11530,7 +11504,7 @@
         <v>35</v>
       </c>
       <c r="G175" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H175" t="s">
         <v>217</v>
@@ -11541,10 +11515,10 @@
         <v>17</v>
       </c>
       <c r="C176" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="D176" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="E176" t="s">
         <v>25</v>
@@ -11553,7 +11527,7 @@
         <v>35</v>
       </c>
       <c r="G176" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H176" t="s">
         <v>217</v>
@@ -11564,10 +11538,10 @@
         <v>17</v>
       </c>
       <c r="C177" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="D177" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="E177" t="s">
         <v>25</v>
@@ -11576,7 +11550,7 @@
         <v>35</v>
       </c>
       <c r="G177" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H177" t="s">
         <v>217</v>
@@ -11587,10 +11561,10 @@
         <v>17</v>
       </c>
       <c r="C178" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="D178" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="E178" t="s">
         <v>25</v>
@@ -11599,7 +11573,7 @@
         <v>35</v>
       </c>
       <c r="G178" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H178" t="s">
         <v>217</v>
@@ -11610,10 +11584,10 @@
         <v>17</v>
       </c>
       <c r="C179" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="D179" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="E179" t="s">
         <v>25</v>
@@ -11622,7 +11596,7 @@
         <v>35</v>
       </c>
       <c r="G179" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H179" t="s">
         <v>217</v>
@@ -11633,10 +11607,10 @@
         <v>17</v>
       </c>
       <c r="C180" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="D180" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="E180" t="s">
         <v>25</v>
@@ -11645,7 +11619,7 @@
         <v>35</v>
       </c>
       <c r="G180" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H180" t="s">
         <v>217</v>
@@ -11656,10 +11630,10 @@
         <v>17</v>
       </c>
       <c r="C181" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="D181" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="E181" t="s">
         <v>25</v>
@@ -11668,7 +11642,7 @@
         <v>35</v>
       </c>
       <c r="G181" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H181" t="s">
         <v>217</v>
@@ -11679,10 +11653,10 @@
         <v>17</v>
       </c>
       <c r="C182" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="D182" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="E182" t="s">
         <v>25</v>
@@ -11691,7 +11665,7 @@
         <v>35</v>
       </c>
       <c r="G182" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H182" t="s">
         <v>217</v>
@@ -11702,10 +11676,10 @@
         <v>17</v>
       </c>
       <c r="C183" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="D183" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="E183" t="s">
         <v>25</v>
@@ -11714,7 +11688,7 @@
         <v>35</v>
       </c>
       <c r="G183" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H183" t="s">
         <v>217</v>
@@ -11725,10 +11699,10 @@
         <v>17</v>
       </c>
       <c r="C184" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="D184" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="E184" t="s">
         <v>25</v>
@@ -11737,7 +11711,7 @@
         <v>35</v>
       </c>
       <c r="G184" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H184" t="s">
         <v>217</v>
@@ -11748,10 +11722,10 @@
         <v>17</v>
       </c>
       <c r="C185" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="D185" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="E185" t="s">
         <v>25</v>
@@ -11760,7 +11734,7 @@
         <v>35</v>
       </c>
       <c r="G185" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H185" t="s">
         <v>217</v>
@@ -11771,10 +11745,10 @@
         <v>17</v>
       </c>
       <c r="C186" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="D186" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="E186" t="s">
         <v>25</v>
@@ -11783,7 +11757,7 @@
         <v>35</v>
       </c>
       <c r="G186" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H186" t="s">
         <v>217</v>
@@ -11794,10 +11768,10 @@
         <v>17</v>
       </c>
       <c r="C187" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="D187" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="E187" t="s">
         <v>25</v>
@@ -11806,7 +11780,7 @@
         <v>35</v>
       </c>
       <c r="G187" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H187" t="s">
         <v>217</v>
@@ -11817,10 +11791,10 @@
         <v>17</v>
       </c>
       <c r="C188" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="D188" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="E188" t="s">
         <v>25</v>
@@ -11829,7 +11803,7 @@
         <v>35</v>
       </c>
       <c r="G188" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H188" t="s">
         <v>217</v>
@@ -11840,10 +11814,10 @@
         <v>17</v>
       </c>
       <c r="C189" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="D189" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="E189" t="s">
         <v>25</v>
@@ -11852,7 +11826,7 @@
         <v>35</v>
       </c>
       <c r="G189" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H189" t="s">
         <v>217</v>
@@ -11863,10 +11837,10 @@
         <v>17</v>
       </c>
       <c r="C190" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="D190" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="E190" t="s">
         <v>25</v>
@@ -11875,7 +11849,7 @@
         <v>35</v>
       </c>
       <c r="G190" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H190" t="s">
         <v>217</v>
@@ -11886,10 +11860,10 @@
         <v>17</v>
       </c>
       <c r="C191" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="D191" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="E191" t="s">
         <v>25</v>
@@ -11898,7 +11872,7 @@
         <v>35</v>
       </c>
       <c r="G191" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H191" t="s">
         <v>217</v>

--- a/VerveStacks_JPN_grids/SysSettings.xlsx
+++ b/VerveStacks_JPN_grids/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4C3C296-8EED-4D1C-9C63-222877A814FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{734066F5-E5AD-4C64-AD70-98C4178A0683}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -7545,7 +7545,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EA3C1FE-2F77-4658-8D9D-9FDCA1B420DF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAB40996-225B-4435-8B23-B1C9E18D89B2}">
   <dimension ref="B3:H191"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SysSettings.xlsx
+++ b/VerveStacks_JPN_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{734066F5-E5AD-4C64-AD70-98C4178A0683}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EE9D6E6-A814-455F-9A00-61BC0591BF48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7545,7 +7545,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAB40996-225B-4435-8B23-B1C9E18D89B2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99F09AFA-3B37-4B73-8FA9-8765A72D6004}">
   <dimension ref="B3:H191"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
